--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\odoo\custom_addons\com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BB9876-9523-40C7-8B0D-DB8228B3378C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BB96D-9BE5-4B57-B5BE-ECC65690BD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14796" yWindow="7548" windowWidth="30612" windowHeight="17004" xr2:uid="{FC0CED0A-9FCE-40DD-BE2D-447C6CC3E712}"/>
+    <workbookView xWindow="10260" yWindow="7200" windowWidth="35148" windowHeight="17352" xr2:uid="{FC0CED0A-9FCE-40DD-BE2D-447C6CC3E712}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="61">
   <si>
     <t>Белая Церковь</t>
   </si>
@@ -225,9 +226,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₴_-;\-* #,##0.00\ _₴_-;_-* &quot;-&quot;??\ _₴_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -268,7 +271,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +306,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E2FF"/>
         <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,7 +615,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -641,7 +650,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -747,6 +755,41 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1083,7 +1126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAC6E24-B730-4B07-BF1F-2046EA212C85}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -1091,967 +1134,1164 @@
     <col min="3" max="4" width="15.88671875" customWidth="1"/>
     <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
     <col min="9" max="12" width="15.6640625" style="1" customWidth="1"/>
     <col min="13" max="15" width="13.33203125" style="2" customWidth="1"/>
     <col min="16" max="16" width="16.6640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="40" t="s">
+      <c r="M1" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="P1" s="40" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="44">
+    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43">
         <v>100</v>
       </c>
-      <c r="H2" s="44"/>
-      <c r="I2" s="45" t="s">
+      <c r="H2" s="43"/>
+      <c r="I2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="45" t="s">
+      <c r="K2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="45" t="s">
+      <c r="L2" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="M2" s="46">
+      <c r="M2" s="45">
         <v>20</v>
       </c>
-      <c r="N2" s="46">
+      <c r="N2" s="45">
         <v>100</v>
       </c>
-      <c r="O2" s="46">
+      <c r="O2" s="45">
         <v>15</v>
       </c>
-      <c r="P2" s="47">
+      <c r="P2" s="46">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="S2" s="48">
+        <f>MAX(R3:R19)</f>
+        <v>2</v>
+      </c>
+      <c r="T2" s="50">
+        <f>MAX(R20:R36)</f>
+        <v>1.3018578713375026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="32">
+        <v>19591959</v>
+      </c>
+      <c r="H3" s="33">
+        <v>23351606.629999999</v>
+      </c>
+      <c r="I3" s="33">
+        <v>340116.97</v>
+      </c>
+      <c r="J3" s="33">
+        <v>905066.28</v>
+      </c>
+      <c r="K3" s="33">
+        <v>1183687.8500000001</v>
+      </c>
+      <c r="L3" s="34">
+        <v>415908.174</v>
+      </c>
+      <c r="M3" s="18">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="N3" s="19">
+        <v>1.5990000000000002E-3</v>
+      </c>
+      <c r="O3" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P3" s="20">
+        <v>2E-3</v>
+      </c>
+      <c r="Q3" s="47">
+        <f>H3*O3</f>
+        <v>1167580.3315000001</v>
+      </c>
+      <c r="R3" s="48">
+        <f>IF(Q3/K3&gt;2,2,Q3/K3)</f>
+        <v>0.98639208935024547</v>
+      </c>
+      <c r="S3" s="49">
+        <f>R3/$S$2*$O$2</f>
+        <v>7.3979406701268413</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="15">
+        <v>1938784</v>
+      </c>
+      <c r="H4" s="16">
+        <v>2507130.58</v>
+      </c>
+      <c r="I4" s="16">
+        <v>906.39</v>
+      </c>
+      <c r="J4" s="16">
+        <v>72053.38</v>
+      </c>
+      <c r="K4" s="16">
+        <v>134775</v>
+      </c>
+      <c r="L4" s="17">
+        <v>12052.344999999999</v>
+      </c>
+      <c r="M4" s="18">
+        <v>1.15E-2</v>
+      </c>
+      <c r="N4" s="19">
+        <v>1.0660000000000001E-3</v>
+      </c>
+      <c r="O4" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P4" s="20">
+        <v>1.03E-2</v>
+      </c>
+      <c r="Q4" s="47">
+        <f t="shared" ref="Q4:Q19" si="0">H4*O4</f>
+        <v>125356.52900000001</v>
+      </c>
+      <c r="R4" s="48">
+        <f t="shared" ref="R4:R36" si="1">IF(Q4/K4&gt;2,2,Q4/K4)</f>
+        <v>0.93011707660916354</v>
+      </c>
+      <c r="S4" s="49">
+        <f t="shared" ref="S4:S19" si="2">R4/$S$2*$O$2</f>
+        <v>6.9758780745687261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="15">
+        <v>22755058</v>
+      </c>
+      <c r="H5" s="16">
+        <v>17154613.550000001</v>
+      </c>
+      <c r="I5" s="16">
+        <v>219251.72</v>
+      </c>
+      <c r="J5" s="16">
+        <v>26162.53</v>
+      </c>
+      <c r="K5" s="16">
+        <v>950479.86</v>
+      </c>
+      <c r="L5" s="17">
+        <v>355339.39600000001</v>
+      </c>
+      <c r="M5" s="18">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="N5" s="19">
+        <v>1.9E-3</v>
+      </c>
+      <c r="O5" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P5" s="20">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="Q5" s="47">
+        <f t="shared" si="0"/>
+        <v>857730.67750000011</v>
+      </c>
+      <c r="R5" s="48">
+        <f t="shared" si="1"/>
+        <v>0.90241857149924265</v>
+      </c>
+      <c r="S5" s="49">
+        <f t="shared" si="2"/>
+        <v>6.7681392862443195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="15">
+        <v>2686986</v>
+      </c>
+      <c r="H6" s="16">
+        <v>3261158.66</v>
+      </c>
+      <c r="I6" s="16">
+        <v>11393.01</v>
+      </c>
+      <c r="J6" s="16">
+        <v>69063.679999999993</v>
+      </c>
+      <c r="K6" s="16">
+        <v>215080.68</v>
+      </c>
+      <c r="L6" s="17">
+        <v>10297.922</v>
+      </c>
+      <c r="M6" s="18">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="N6" s="19">
+        <v>1.9E-3</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P6" s="20">
+        <v>6.1999999999999998E-3</v>
+      </c>
+      <c r="Q6" s="47">
+        <f t="shared" si="0"/>
+        <v>163057.93300000002</v>
+      </c>
+      <c r="R6" s="48">
+        <f t="shared" si="1"/>
+        <v>0.75812450007132215</v>
+      </c>
+      <c r="S6" s="49">
+        <f t="shared" si="2"/>
+        <v>5.6859337505349163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="15">
+        <v>9091366</v>
+      </c>
+      <c r="H7" s="16">
+        <v>8996043.75</v>
+      </c>
+      <c r="I7" s="16">
+        <v>152767.69</v>
+      </c>
+      <c r="J7" s="16">
+        <v>7136.64</v>
+      </c>
+      <c r="K7" s="16">
+        <v>634099.98</v>
+      </c>
+      <c r="L7" s="17">
+        <v>280739.12400000001</v>
+      </c>
+      <c r="M7" s="18">
+        <v>1.34E-2</v>
+      </c>
+      <c r="N7" s="19">
+        <v>3.1980000000000003E-3</v>
+      </c>
+      <c r="O7" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P7" s="20">
+        <v>3.9000000000000003E-3</v>
+      </c>
+      <c r="Q7" s="47">
+        <f t="shared" si="0"/>
+        <v>449802.1875</v>
+      </c>
+      <c r="R7" s="48">
+        <f t="shared" si="1"/>
+        <v>0.7093553093945848</v>
+      </c>
+      <c r="S7" s="49">
+        <f t="shared" si="2"/>
+        <v>5.3201648204593859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="15">
+        <v>6743579</v>
+      </c>
+      <c r="H8" s="16">
+        <v>6642878.6900000004</v>
+      </c>
+      <c r="I8" s="16">
+        <v>3409.33</v>
+      </c>
+      <c r="J8" s="16">
+        <v>65470.52</v>
+      </c>
+      <c r="K8" s="16">
+        <v>407617.55</v>
+      </c>
+      <c r="L8" s="17">
+        <v>91207.59</v>
+      </c>
+      <c r="M8" s="18">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N8" s="19">
+        <v>1.0660000000000001E-3</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P8" s="20">
+        <v>1.1000000000000001E-2</v>
+      </c>
+      <c r="Q8" s="47">
+        <f t="shared" si="0"/>
+        <v>332143.93450000003</v>
+      </c>
+      <c r="R8" s="48">
+        <f t="shared" si="1"/>
+        <v>0.81484208543032566</v>
+      </c>
+      <c r="S8" s="49">
+        <f t="shared" si="2"/>
+        <v>6.111315640727442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="33">
-        <v>19591959</v>
-      </c>
-      <c r="H3" s="34">
-        <v>23351606.629999999</v>
-      </c>
-      <c r="I3" s="34">
-        <v>340116.97</v>
-      </c>
-      <c r="J3" s="34">
-        <v>905066.28</v>
-      </c>
-      <c r="K3" s="34">
-        <v>1183687.8500000001</v>
-      </c>
-      <c r="L3" s="35">
-        <v>415908.174</v>
-      </c>
-      <c r="M3" s="19">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="N3" s="20">
+      <c r="C9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="15">
+        <v>15993683</v>
+      </c>
+      <c r="H9" s="16">
+        <v>16522919.58</v>
+      </c>
+      <c r="I9" s="16">
+        <v>146350.9</v>
+      </c>
+      <c r="J9" s="16">
+        <v>167073.5</v>
+      </c>
+      <c r="K9" s="16">
+        <v>4292</v>
+      </c>
+      <c r="L9" s="17">
+        <v>320983.74400000001</v>
+      </c>
+      <c r="M9" s="18">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="N9" s="19">
+        <v>2.6650000000000003E-3</v>
+      </c>
+      <c r="O9" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P9" s="20">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="Q9" s="47">
+        <f>H9*O9</f>
+        <v>826145.97900000005</v>
+      </c>
+      <c r="R9" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S9" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="15">
+        <v>3868280</v>
+      </c>
+      <c r="H10" s="16">
+        <v>4053690.1</v>
+      </c>
+      <c r="I10" s="16">
+        <v>30464.93</v>
+      </c>
+      <c r="J10" s="16">
+        <v>67225.78</v>
+      </c>
+      <c r="K10" s="16">
+        <v>210065</v>
+      </c>
+      <c r="L10" s="17">
+        <v>37777.313999999998</v>
+      </c>
+      <c r="M10" s="18">
+        <v>9.0000000000000011E-3</v>
+      </c>
+      <c r="N10" s="19">
         <v>1.5990000000000002E-3</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O10" s="19">
         <v>0.05</v>
       </c>
-      <c r="P3" s="21">
-        <v>2E-3</v>
-      </c>
-      <c r="Q3" s="12"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="P10" s="20">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="Q10" s="47">
+        <f t="shared" si="0"/>
+        <v>202684.505</v>
+      </c>
+      <c r="R10" s="48">
+        <f t="shared" si="1"/>
+        <v>0.96486566062885304</v>
+      </c>
+      <c r="S10" s="49">
+        <f t="shared" si="2"/>
+        <v>7.236492454716398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="C11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="15">
+        <v>19794522</v>
+      </c>
+      <c r="H11" s="16">
+        <v>20005520.420000002</v>
+      </c>
+      <c r="I11" s="16">
+        <v>188212.22</v>
+      </c>
+      <c r="J11" s="16">
+        <v>223063.28</v>
+      </c>
+      <c r="K11" s="16">
+        <v>6860</v>
+      </c>
+      <c r="L11" s="17">
+        <v>140024.65</v>
+      </c>
+      <c r="M11" s="18">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="N11" s="19">
+        <v>1.0660000000000001E-3</v>
+      </c>
+      <c r="O11" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="P11" s="20">
+        <v>4.8999999999999998E-3</v>
+      </c>
+      <c r="Q11" s="47">
+        <f t="shared" si="0"/>
+        <v>1000276.0210000002</v>
+      </c>
+      <c r="R11" s="48">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="16">
-        <v>1938784</v>
-      </c>
-      <c r="H4" s="17">
-        <v>2507130.58</v>
-      </c>
-      <c r="I4" s="17">
-        <v>906.39</v>
-      </c>
-      <c r="J4" s="17">
-        <v>72053.38</v>
-      </c>
-      <c r="K4" s="17">
-        <v>134775</v>
-      </c>
-      <c r="L4" s="18">
-        <v>12052.344999999999</v>
-      </c>
-      <c r="M4" s="19">
-        <v>1.15E-2</v>
-      </c>
-      <c r="N4" s="20">
+      <c r="S11" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="15">
+        <v>21909086</v>
+      </c>
+      <c r="H12" s="16">
+        <v>22951289.809999999</v>
+      </c>
+      <c r="I12" s="16">
+        <v>208685.61</v>
+      </c>
+      <c r="J12" s="16">
+        <v>7435.1</v>
+      </c>
+      <c r="K12" s="16">
+        <v>16540</v>
+      </c>
+      <c r="L12" s="17">
+        <v>408158.78700000001</v>
+      </c>
+      <c r="M12" s="18">
+        <v>6.8000000000000005E-3</v>
+      </c>
+      <c r="N12" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O12" s="19">
         <v>0.05</v>
       </c>
-      <c r="P4" s="21">
-        <v>1.03E-2</v>
-      </c>
-      <c r="Q4" s="12"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="P12" s="20">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="Q12" s="47">
+        <f t="shared" si="0"/>
+        <v>1147564.4905000001</v>
+      </c>
+      <c r="R12" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S12" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="16">
-        <v>22755058</v>
-      </c>
-      <c r="H5" s="17">
-        <v>17154613.550000001</v>
-      </c>
-      <c r="I5" s="17">
-        <v>219251.72</v>
-      </c>
-      <c r="J5" s="17">
-        <v>26162.53</v>
-      </c>
-      <c r="K5" s="17">
-        <v>950479.86</v>
-      </c>
-      <c r="L5" s="18">
-        <v>355339.39600000001</v>
-      </c>
-      <c r="M5" s="19">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="N5" s="20">
-        <v>1.9E-3</v>
-      </c>
-      <c r="O5" s="20">
+      <c r="C13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="15">
+        <v>17009357</v>
+      </c>
+      <c r="H13" s="16">
+        <v>17127476.359999999</v>
+      </c>
+      <c r="I13" s="16">
+        <v>124955.03</v>
+      </c>
+      <c r="J13" s="16">
+        <v>190824.85</v>
+      </c>
+      <c r="K13" s="16">
+        <v>13718</v>
+      </c>
+      <c r="L13" s="17">
+        <v>129564.88499999999</v>
+      </c>
+      <c r="M13" s="18">
+        <v>6.8000000000000005E-3</v>
+      </c>
+      <c r="N13" s="19">
+        <v>1.0660000000000001E-3</v>
+      </c>
+      <c r="O13" s="19">
         <v>0.05</v>
       </c>
-      <c r="P5" s="21">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="Q5" s="12"/>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="P13" s="20">
+        <v>3.9000000000000003E-3</v>
+      </c>
+      <c r="Q13" s="47">
+        <f t="shared" si="0"/>
+        <v>856373.81799999997</v>
+      </c>
+      <c r="R13" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S13" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="16">
-        <v>2686986</v>
-      </c>
-      <c r="H6" s="17">
-        <v>3261158.66</v>
-      </c>
-      <c r="I6" s="17">
-        <v>11393.01</v>
-      </c>
-      <c r="J6" s="17">
-        <v>69063.679999999993</v>
-      </c>
-      <c r="K6" s="17">
-        <v>215080.68</v>
-      </c>
-      <c r="L6" s="18">
-        <v>10297.922</v>
-      </c>
-      <c r="M6" s="19">
-        <v>7.7000000000000002E-3</v>
-      </c>
-      <c r="N6" s="20">
-        <v>1.9E-3</v>
-      </c>
-      <c r="O6" s="20">
+      <c r="C14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="15">
+        <v>24798734</v>
+      </c>
+      <c r="H14" s="16">
+        <v>26507855.93</v>
+      </c>
+      <c r="I14" s="16">
+        <v>93468.95</v>
+      </c>
+      <c r="J14" s="16">
+        <v>26600.69</v>
+      </c>
+      <c r="K14" s="16">
+        <v>475842</v>
+      </c>
+      <c r="L14" s="17">
+        <v>207175.95800000001</v>
+      </c>
+      <c r="M14" s="18">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="N14" s="19">
+        <v>1.0660000000000001E-3</v>
+      </c>
+      <c r="O14" s="19">
         <v>0.05</v>
       </c>
-      <c r="P6" s="21">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="Q6" s="12"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="P14" s="20">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="Q14" s="47">
+        <f t="shared" si="0"/>
+        <v>1325392.7965000002</v>
+      </c>
+      <c r="R14" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S14" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="16">
-        <v>9091366</v>
-      </c>
-      <c r="H7" s="17">
-        <v>8996043.75</v>
-      </c>
-      <c r="I7" s="17">
-        <v>152767.69</v>
-      </c>
-      <c r="J7" s="17">
-        <v>7136.64</v>
-      </c>
-      <c r="K7" s="17">
-        <v>634099.98</v>
-      </c>
-      <c r="L7" s="18">
-        <v>280739.12400000001</v>
-      </c>
-      <c r="M7" s="19">
-        <v>1.34E-2</v>
-      </c>
-      <c r="N7" s="20">
+      <c r="B15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="15">
+        <v>6856551</v>
+      </c>
+      <c r="H15" s="16">
+        <v>6716259.54</v>
+      </c>
+      <c r="I15" s="16">
+        <v>83542.95</v>
+      </c>
+      <c r="J15" s="16">
+        <v>134250.79999999999</v>
+      </c>
+      <c r="K15" s="16">
+        <v>226615</v>
+      </c>
+      <c r="L15" s="17">
+        <v>262618.62</v>
+      </c>
+      <c r="M15" s="18">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="N15" s="19">
         <v>3.1980000000000003E-3</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O15" s="19">
         <v>0.05</v>
       </c>
-      <c r="P7" s="21">
-        <v>3.9000000000000003E-3</v>
-      </c>
-      <c r="Q7" s="12"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="P15" s="20">
+        <v>1.23E-2</v>
+      </c>
+      <c r="Q15" s="47">
+        <f t="shared" si="0"/>
+        <v>335812.97700000001</v>
+      </c>
+      <c r="R15" s="48">
+        <f t="shared" si="1"/>
+        <v>1.4818656178981975</v>
+      </c>
+      <c r="S15" s="49">
+        <f t="shared" si="2"/>
+        <v>11.113992134236481</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="16">
-        <v>6743579</v>
-      </c>
-      <c r="H8" s="17">
-        <v>6642878.6900000004</v>
-      </c>
-      <c r="I8" s="17">
-        <v>3409.33</v>
-      </c>
-      <c r="J8" s="17">
-        <v>65470.52</v>
-      </c>
-      <c r="K8" s="17">
-        <v>407617.55</v>
-      </c>
-      <c r="L8" s="18">
-        <v>91207.59</v>
-      </c>
-      <c r="M8" s="19">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="N8" s="20">
-        <v>1.0660000000000001E-3</v>
-      </c>
-      <c r="O8" s="20">
+      <c r="B16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="15">
+        <v>30621195</v>
+      </c>
+      <c r="H16" s="16">
+        <v>32052691.809999999</v>
+      </c>
+      <c r="I16" s="16">
+        <v>186262.07</v>
+      </c>
+      <c r="J16" s="16">
+        <v>24274.43</v>
+      </c>
+      <c r="K16" s="16">
+        <v>1244568</v>
+      </c>
+      <c r="L16" s="17">
+        <v>332994.59499999997</v>
+      </c>
+      <c r="M16" s="18">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="N16" s="19">
+        <v>2.1320000000000002E-3</v>
+      </c>
+      <c r="O16" s="19">
         <v>0.05</v>
       </c>
-      <c r="P8" s="21">
-        <v>1.1000000000000001E-2</v>
-      </c>
-      <c r="Q8" s="12"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="P16" s="20">
+        <v>1E-3</v>
+      </c>
+      <c r="Q16" s="47">
+        <f t="shared" si="0"/>
+        <v>1602634.5904999999</v>
+      </c>
+      <c r="R16" s="48">
+        <f t="shared" si="1"/>
+        <v>1.2877035168026174</v>
+      </c>
+      <c r="S16" s="49">
+        <f t="shared" si="2"/>
+        <v>9.6577763760196298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="16">
-        <v>15993683</v>
-      </c>
-      <c r="H9" s="17">
-        <v>16522919.58</v>
-      </c>
-      <c r="I9" s="17">
-        <v>146350.9</v>
-      </c>
-      <c r="J9" s="17">
-        <v>167073.5</v>
-      </c>
-      <c r="K9" s="17">
-        <v>4292</v>
-      </c>
-      <c r="L9" s="18">
-        <v>320983.74400000001</v>
-      </c>
-      <c r="M9" s="19">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="N9" s="20">
+      <c r="E17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="15">
+        <v>17188836</v>
+      </c>
+      <c r="H17" s="16">
+        <v>17428018.870000001</v>
+      </c>
+      <c r="I17" s="16">
+        <v>116216.48</v>
+      </c>
+      <c r="J17" s="16">
+        <v>259230.85</v>
+      </c>
+      <c r="K17" s="16">
+        <v>431095</v>
+      </c>
+      <c r="L17" s="17">
+        <v>141745.95499999999</v>
+      </c>
+      <c r="M17" s="18">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="N17" s="19">
         <v>2.6650000000000003E-3</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O17" s="19">
         <v>0.05</v>
       </c>
-      <c r="P9" s="21">
-        <v>4.5999999999999999E-3</v>
-      </c>
-      <c r="Q9" s="12"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="P17" s="20">
+        <v>2.8000000000000004E-3</v>
+      </c>
+      <c r="Q17" s="47">
+        <f t="shared" si="0"/>
+        <v>871400.94350000005</v>
+      </c>
+      <c r="R17" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S17" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="16">
-        <v>3868280</v>
-      </c>
-      <c r="H10" s="17">
-        <v>4053690.1</v>
-      </c>
-      <c r="I10" s="17">
-        <v>30464.93</v>
-      </c>
-      <c r="J10" s="17">
-        <v>67225.78</v>
-      </c>
-      <c r="K10" s="17">
-        <v>210065</v>
-      </c>
-      <c r="L10" s="18">
-        <v>37777.313999999998</v>
-      </c>
-      <c r="M10" s="19">
-        <v>9.0000000000000011E-3</v>
-      </c>
-      <c r="N10" s="20">
+      <c r="E18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1219932</v>
+      </c>
+      <c r="H18" s="16">
+        <v>1151560.95</v>
+      </c>
+      <c r="I18" s="16">
+        <v>31147.97</v>
+      </c>
+      <c r="J18" s="16">
+        <v>55662.48</v>
+      </c>
+      <c r="K18" s="16">
+        <v>8988</v>
+      </c>
+      <c r="L18" s="17">
+        <v>39011.692999999999</v>
+      </c>
+      <c r="M18" s="18">
+        <v>8.1000000000000013E-3</v>
+      </c>
+      <c r="N18" s="19">
         <v>1.5990000000000002E-3</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O18" s="19">
         <v>0.05</v>
       </c>
-      <c r="P10" s="21">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q10" s="12"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="P18" s="20">
+        <v>1.55E-2</v>
+      </c>
+      <c r="Q18" s="47">
+        <f t="shared" si="0"/>
+        <v>57578.047500000001</v>
+      </c>
+      <c r="R18" s="48">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S18" s="49">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B19" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C19" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D19" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="16">
-        <v>19794522</v>
-      </c>
-      <c r="H11" s="17">
-        <v>20005520.420000002</v>
-      </c>
-      <c r="I11" s="17">
-        <v>188212.22</v>
-      </c>
-      <c r="J11" s="17">
-        <v>223063.28</v>
-      </c>
-      <c r="K11" s="17">
-        <v>6860</v>
-      </c>
-      <c r="L11" s="18">
-        <v>140024.65</v>
-      </c>
-      <c r="M11" s="19">
-        <v>5.7999999999999996E-3</v>
-      </c>
-      <c r="N11" s="20">
-        <v>1.0660000000000001E-3</v>
-      </c>
-      <c r="O11" s="20">
+      <c r="E19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="24">
+        <v>3312987</v>
+      </c>
+      <c r="H19" s="25">
+        <v>3213559.51</v>
+      </c>
+      <c r="I19" s="25">
+        <v>28816.78</v>
+      </c>
+      <c r="J19" s="25">
+        <v>3780.6</v>
+      </c>
+      <c r="K19" s="25">
+        <v>205547</v>
+      </c>
+      <c r="L19" s="26">
+        <v>68784.183000000005</v>
+      </c>
+      <c r="M19" s="27">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="N19" s="28">
+        <v>3.1980000000000003E-3</v>
+      </c>
+      <c r="O19" s="28">
         <v>0.05</v>
       </c>
-      <c r="P11" s="21">
-        <v>4.8999999999999998E-3</v>
-      </c>
-      <c r="Q11" s="12"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="16">
-        <v>21909086</v>
-      </c>
-      <c r="H12" s="17">
-        <v>22951289.809999999</v>
-      </c>
-      <c r="I12" s="17">
-        <v>208685.61</v>
-      </c>
-      <c r="J12" s="17">
-        <v>7435.1</v>
-      </c>
-      <c r="K12" s="17">
-        <v>16540</v>
-      </c>
-      <c r="L12" s="18">
-        <v>408158.78700000001</v>
-      </c>
-      <c r="M12" s="19">
-        <v>6.8000000000000005E-3</v>
-      </c>
-      <c r="N12" s="20">
-        <v>1.0660000000000001E-3</v>
-      </c>
-      <c r="O12" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P12" s="21">
-        <v>3.2000000000000002E-3</v>
-      </c>
-      <c r="Q12" s="12"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="16">
-        <v>17009357</v>
-      </c>
-      <c r="H13" s="17">
-        <v>17127476.359999999</v>
-      </c>
-      <c r="I13" s="17">
-        <v>124955.03</v>
-      </c>
-      <c r="J13" s="17">
-        <v>190824.85</v>
-      </c>
-      <c r="K13" s="17">
-        <v>13718</v>
-      </c>
-      <c r="L13" s="18">
-        <v>129564.88499999999</v>
-      </c>
-      <c r="M13" s="19">
-        <v>6.8000000000000005E-3</v>
-      </c>
-      <c r="N13" s="20">
-        <v>1.0660000000000001E-3</v>
-      </c>
-      <c r="O13" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P13" s="21">
-        <v>3.9000000000000003E-3</v>
-      </c>
-      <c r="Q13" s="12"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="16">
-        <v>24798734</v>
-      </c>
-      <c r="H14" s="17">
-        <v>26507855.93</v>
-      </c>
-      <c r="I14" s="17">
-        <v>93468.95</v>
-      </c>
-      <c r="J14" s="17">
-        <v>26600.69</v>
-      </c>
-      <c r="K14" s="17">
-        <v>475842</v>
-      </c>
-      <c r="L14" s="18">
-        <v>207175.95800000001</v>
-      </c>
-      <c r="M14" s="19">
-        <v>3.0999999999999999E-3</v>
-      </c>
-      <c r="N14" s="20">
-        <v>1.0660000000000001E-3</v>
-      </c>
-      <c r="O14" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P14" s="21">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="Q14" s="12"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="16">
-        <v>6856551</v>
-      </c>
-      <c r="H15" s="17">
-        <v>6716259.54</v>
-      </c>
-      <c r="I15" s="17">
-        <v>83542.95</v>
-      </c>
-      <c r="J15" s="17">
-        <v>134250.79999999999</v>
-      </c>
-      <c r="K15" s="17">
-        <v>226615</v>
-      </c>
-      <c r="L15" s="18">
-        <v>262618.62</v>
-      </c>
-      <c r="M15" s="19">
-        <v>9.7000000000000003E-3</v>
-      </c>
-      <c r="N15" s="20">
-        <v>3.1980000000000003E-3</v>
-      </c>
-      <c r="O15" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P15" s="21">
-        <v>1.23E-2</v>
-      </c>
-      <c r="Q15" s="12"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="16">
-        <v>30621195</v>
-      </c>
-      <c r="H16" s="17">
-        <v>32052691.809999999</v>
-      </c>
-      <c r="I16" s="17">
-        <v>186262.07</v>
-      </c>
-      <c r="J16" s="17">
-        <v>24274.43</v>
-      </c>
-      <c r="K16" s="17">
-        <v>1244568</v>
-      </c>
-      <c r="L16" s="18">
-        <v>332994.59499999997</v>
-      </c>
-      <c r="M16" s="19">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="N16" s="20">
-        <v>2.1320000000000002E-3</v>
-      </c>
-      <c r="O16" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P16" s="21">
-        <v>1E-3</v>
-      </c>
-      <c r="Q16" s="12"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="16">
-        <v>17188836</v>
-      </c>
-      <c r="H17" s="17">
-        <v>17428018.870000001</v>
-      </c>
-      <c r="I17" s="17">
-        <v>116216.48</v>
-      </c>
-      <c r="J17" s="17">
-        <v>259230.85</v>
-      </c>
-      <c r="K17" s="17">
-        <v>431095</v>
-      </c>
-      <c r="L17" s="18">
-        <v>141745.95499999999</v>
-      </c>
-      <c r="M17" s="19">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="N17" s="20">
-        <v>2.6650000000000003E-3</v>
-      </c>
-      <c r="O17" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P17" s="21">
-        <v>2.8000000000000004E-3</v>
-      </c>
-      <c r="Q17" s="12"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" s="16">
-        <v>1219932</v>
-      </c>
-      <c r="H18" s="17">
-        <v>1151560.95</v>
-      </c>
-      <c r="I18" s="17">
-        <v>31147.97</v>
-      </c>
-      <c r="J18" s="17">
-        <v>55662.48</v>
-      </c>
-      <c r="K18" s="17">
-        <v>8988</v>
-      </c>
-      <c r="L18" s="18">
-        <v>39011.692999999999</v>
-      </c>
-      <c r="M18" s="19">
-        <v>8.1000000000000013E-3</v>
-      </c>
-      <c r="N18" s="20">
-        <v>1.5990000000000002E-3</v>
-      </c>
-      <c r="O18" s="20">
-        <v>0.05</v>
-      </c>
-      <c r="P18" s="21">
-        <v>1.55E-2</v>
-      </c>
-      <c r="Q18" s="12"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="25">
-        <v>3312987</v>
-      </c>
-      <c r="H19" s="26">
-        <v>3213559.51</v>
-      </c>
-      <c r="I19" s="26">
-        <v>28816.78</v>
-      </c>
-      <c r="J19" s="26">
-        <v>3780.6</v>
-      </c>
-      <c r="K19" s="26">
-        <v>205547</v>
-      </c>
-      <c r="L19" s="27">
-        <v>68784.183000000005</v>
-      </c>
-      <c r="M19" s="28">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="N19" s="29">
-        <v>3.1980000000000003E-3</v>
-      </c>
-      <c r="O19" s="29">
-        <v>0.05</v>
-      </c>
-      <c r="P19" s="30">
+      <c r="P19" s="29">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="Q19" s="12"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q19" s="47">
+        <f t="shared" si="0"/>
+        <v>160677.9755</v>
+      </c>
+      <c r="R19" s="48">
+        <f t="shared" si="1"/>
+        <v>0.78170917357100811</v>
+      </c>
+      <c r="S19" s="49">
+        <f t="shared" si="2"/>
+        <v>5.8628188017825611</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
@@ -2100,821 +2340,1009 @@
       <c r="P20" s="11">
         <v>2E-3</v>
       </c>
-      <c r="Q20" s="12"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="Q20" s="47">
+        <f t="shared" ref="Q20:Q36" si="3">H20*O20</f>
+        <v>1118890.236</v>
+      </c>
+      <c r="R20" s="48">
+        <f t="shared" si="1"/>
+        <v>0.99083804296930778</v>
+      </c>
+      <c r="S20" s="49">
+        <f>R20/$T$2*$O$2</f>
+        <v>11.416431064990304</v>
+      </c>
+      <c r="T20" s="48"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="15">
         <v>2100233</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="16">
         <v>2296569.0099999998</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="16">
         <v>2450.86</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="16">
         <v>22035.74</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>112435</v>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="17">
         <v>16538.763999999999</v>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="18">
         <v>1.15E-2</v>
       </c>
-      <c r="N21" s="20">
+      <c r="N21" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O21" s="20">
+      <c r="O21" s="19">
         <v>0.05</v>
       </c>
-      <c r="P21" s="21">
+      <c r="P21" s="20">
         <v>1.03E-2</v>
       </c>
-      <c r="Q21" s="12"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="Q21" s="47">
+        <f t="shared" si="3"/>
+        <v>114828.45049999999</v>
+      </c>
+      <c r="R21" s="48">
+        <f t="shared" si="1"/>
+        <v>1.0212874149508604</v>
+      </c>
+      <c r="S21" s="49">
+        <f t="shared" ref="S21:S36" si="4">R21/$T$2*$O$2</f>
+        <v>11.767268579421925</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="15">
         <v>6000000</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="16">
         <v>8754757.2799999993</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="16">
         <v>2613.98</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="16">
         <v>11687.46</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>881288</v>
       </c>
-      <c r="L22" s="18">
+      <c r="L22" s="17">
         <v>4645.74</v>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="18">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="N22" s="20">
+      <c r="N22" s="19">
         <v>1.9E-3</v>
       </c>
-      <c r="O22" s="20">
+      <c r="O22" s="19">
         <v>0.05</v>
       </c>
-      <c r="P22" s="21">
+      <c r="P22" s="20">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="Q22" s="12"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="Q22" s="47">
+        <f t="shared" si="3"/>
+        <v>437737.864</v>
+      </c>
+      <c r="R22" s="48">
+        <f t="shared" si="1"/>
+        <v>0.49670239921569337</v>
+      </c>
+      <c r="S22" s="49">
+        <f t="shared" si="4"/>
+        <v>5.7230026044093965</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <v>3232951</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <v>3156377.33</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="16">
         <v>8713.2800000000007</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="16">
         <v>96077.08</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="16">
         <v>193900</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="17">
         <v>22909.393</v>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="18">
         <v>7.7000000000000002E-3</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="19">
         <v>1.9E-3</v>
       </c>
-      <c r="O23" s="20">
+      <c r="O23" s="19">
         <v>0.05</v>
       </c>
-      <c r="P23" s="21">
+      <c r="P23" s="20">
         <v>6.1999999999999998E-3</v>
       </c>
-      <c r="Q23" s="12"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="Q23" s="47">
+        <f t="shared" si="3"/>
+        <v>157818.8665</v>
+      </c>
+      <c r="R23" s="48">
+        <f t="shared" si="1"/>
+        <v>0.81391885765858696</v>
+      </c>
+      <c r="S23" s="49">
+        <f t="shared" si="4"/>
+        <v>9.3779690807075173</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <v>8508152</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <v>8782254.2200000007</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="16">
         <v>114550.21</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="16">
         <v>215004.99</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="16">
         <v>560636.86</v>
       </c>
-      <c r="L24" s="18">
+      <c r="L24" s="17">
         <v>17399.486000000001</v>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="18">
         <v>1.34E-2</v>
       </c>
-      <c r="N24" s="20">
+      <c r="N24" s="19">
         <v>3.1980000000000003E-3</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="19">
         <v>0.05</v>
       </c>
-      <c r="P24" s="21">
+      <c r="P24" s="20">
         <v>3.9000000000000003E-3</v>
       </c>
-      <c r="Q24" s="12"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="Q24" s="47">
+        <f t="shared" si="3"/>
+        <v>439112.71100000007</v>
+      </c>
+      <c r="R24" s="48">
+        <f t="shared" si="1"/>
+        <v>0.78323910240222183</v>
+      </c>
+      <c r="S24" s="49">
+        <f t="shared" si="4"/>
+        <v>9.0244770913149406</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <v>6150356</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="16">
         <v>6331291.4800000004</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="16">
         <v>848.46</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="16">
         <v>55561.33</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>357491.39</v>
       </c>
-      <c r="L25" s="18">
+      <c r="L25" s="17">
         <v>7466.04</v>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="18">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="N25" s="20">
+      <c r="N25" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25" s="19">
         <v>0.05</v>
       </c>
-      <c r="P25" s="21">
+      <c r="P25" s="20">
         <v>1.1000000000000001E-2</v>
       </c>
-      <c r="Q25" s="12"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="Q25" s="47">
+        <f t="shared" si="3"/>
+        <v>316564.57400000002</v>
+      </c>
+      <c r="R25" s="48">
+        <f t="shared" si="1"/>
+        <v>0.88551663859652674</v>
+      </c>
+      <c r="S25" s="49">
+        <f t="shared" si="4"/>
+        <v>10.20291836105079</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="15">
         <v>15306555</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="16">
         <v>15570538.48</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="16">
         <v>175447.9</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="16">
         <v>272389.03000000003</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="16">
         <v>787796.12</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="17">
         <v>30519.866999999998</v>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="18">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="N26" s="20">
+      <c r="N26" s="19">
         <v>2.6650000000000003E-3</v>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="19">
         <v>0.05</v>
       </c>
-      <c r="P26" s="21">
+      <c r="P26" s="20">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="Q26" s="12"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="Q26" s="47">
+        <f t="shared" si="3"/>
+        <v>778526.92400000012</v>
+      </c>
+      <c r="R26" s="48">
+        <f t="shared" si="1"/>
+        <v>0.98823401668949595</v>
+      </c>
+      <c r="S26" s="49">
+        <f t="shared" si="4"/>
+        <v>11.386427486982939</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="15">
         <v>3762746</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <v>3787951.38</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="16">
         <v>46493.04</v>
       </c>
-      <c r="J27" s="17">
+      <c r="J27" s="16">
         <v>76596.06</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="16">
         <v>218845.31</v>
       </c>
-      <c r="L27" s="18">
+      <c r="L27" s="17">
         <v>7222.8</v>
       </c>
-      <c r="M27" s="19">
+      <c r="M27" s="18">
         <v>9.0000000000000011E-3</v>
       </c>
-      <c r="N27" s="20">
+      <c r="N27" s="19">
         <v>1.5990000000000002E-3</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="19">
         <v>0.05</v>
       </c>
-      <c r="P27" s="21">
+      <c r="P27" s="20">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q27" s="12"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="Q27" s="47">
+        <f t="shared" si="3"/>
+        <v>189397.56900000002</v>
+      </c>
+      <c r="R27" s="48">
+        <f t="shared" si="1"/>
+        <v>0.8654403834379637</v>
+      </c>
+      <c r="S27" s="49">
+        <f t="shared" si="4"/>
+        <v>9.9715998477102694</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="15">
         <v>18026002</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="16">
         <v>19295921.5</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="16">
         <v>173219.16</v>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="16">
         <v>10841.97</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="16">
         <v>918662.31</v>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="17">
         <v>19952.25</v>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="18">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="N28" s="20">
+      <c r="N28" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="19">
         <v>0.05</v>
       </c>
-      <c r="P28" s="21">
+      <c r="P28" s="20">
         <v>4.8999999999999998E-3</v>
       </c>
-      <c r="Q28" s="12"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="Q28" s="47">
+        <f t="shared" si="3"/>
+        <v>964796.07500000007</v>
+      </c>
+      <c r="R28" s="48">
+        <f t="shared" si="1"/>
+        <v>1.0502184148601894</v>
+      </c>
+      <c r="S28" s="49">
+        <f t="shared" si="4"/>
+        <v>12.100611418294257</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="15">
         <v>21282486</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="16">
         <v>21928287.18</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="16">
         <v>245143.75</v>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="16">
         <v>258047.3</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="16">
         <v>1075360.1000000001</v>
       </c>
-      <c r="L29" s="18">
+      <c r="L29" s="17">
         <v>30274.82</v>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="18">
         <v>6.8000000000000005E-3</v>
       </c>
-      <c r="N29" s="20">
+      <c r="N29" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="19">
         <v>0.05</v>
       </c>
-      <c r="P29" s="21">
+      <c r="P29" s="20">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="Q29" s="12"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="Q29" s="47">
+        <f t="shared" si="3"/>
+        <v>1096414.3589999999</v>
+      </c>
+      <c r="R29" s="48">
+        <f t="shared" si="1"/>
+        <v>1.0195787987670362</v>
+      </c>
+      <c r="S29" s="49">
+        <f t="shared" si="4"/>
+        <v>11.747581912143081</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="54">
         <v>16421348</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="55">
         <v>16592421.289999999</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="55">
         <v>166414.34</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="55">
         <v>21085.25</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="55">
         <v>775214.89</v>
       </c>
-      <c r="L30" s="18">
+      <c r="L30" s="56">
         <v>24702.48</v>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="57">
         <v>6.8000000000000005E-3</v>
       </c>
-      <c r="N30" s="20">
+      <c r="N30" s="58">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O30" s="20">
+      <c r="O30" s="58">
         <v>0.05</v>
       </c>
-      <c r="P30" s="21">
+      <c r="P30" s="59">
         <v>3.9000000000000003E-3</v>
       </c>
-      <c r="Q30" s="12"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+      <c r="Q30" s="60">
+        <f t="shared" si="3"/>
+        <v>829621.06449999998</v>
+      </c>
+      <c r="R30" s="61">
+        <f t="shared" si="1"/>
+        <v>1.0701820555846133</v>
+      </c>
+      <c r="S30" s="62">
+        <f t="shared" si="4"/>
+        <v>12.330632388677689</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="15">
         <v>24394317</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>24732366.73</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>138177.79</v>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="16">
         <v>19775.87</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="16">
         <v>949887.36</v>
       </c>
-      <c r="L31" s="18">
+      <c r="L31" s="17">
         <v>20745.919999999998</v>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="18">
         <v>3.0999999999999999E-3</v>
       </c>
-      <c r="N31" s="20">
+      <c r="N31" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="19">
         <v>0.05</v>
       </c>
-      <c r="P31" s="21">
+      <c r="P31" s="20">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q31" s="12"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+      <c r="Q31" s="47">
+        <f t="shared" si="3"/>
+        <v>1236618.3365</v>
+      </c>
+      <c r="R31" s="48">
+        <f t="shared" si="1"/>
+        <v>1.3018578713375026</v>
+      </c>
+      <c r="S31" s="49">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="15">
         <v>7182566</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>6727481.3700000001</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <v>85377.279999999999</v>
       </c>
-      <c r="J32" s="17">
+      <c r="J32" s="16">
         <v>167922.88</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K32" s="16">
         <v>464714.09</v>
       </c>
-      <c r="L32" s="18">
+      <c r="L32" s="17">
         <v>54583.16</v>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="18">
         <v>9.7000000000000003E-3</v>
       </c>
-      <c r="N32" s="20">
+      <c r="N32" s="19">
         <v>3.1980000000000003E-3</v>
       </c>
-      <c r="O32" s="20">
+      <c r="O32" s="19">
         <v>0.05</v>
       </c>
-      <c r="P32" s="21">
+      <c r="P32" s="20">
         <v>1.23E-2</v>
       </c>
-      <c r="Q32" s="12"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
+      <c r="Q32" s="47">
+        <f t="shared" si="3"/>
+        <v>336374.06850000005</v>
+      </c>
+      <c r="R32" s="48">
+        <f t="shared" si="1"/>
+        <v>0.72383014790879274</v>
+      </c>
+      <c r="S32" s="49">
+        <f t="shared" si="4"/>
+        <v>8.3399674094048102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="15">
         <v>28067946</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <v>30236809.890000001</v>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="16">
         <v>235038.9</v>
       </c>
-      <c r="J33" s="17">
+      <c r="J33" s="16">
         <v>405668.69</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="16">
         <v>1233206.29</v>
       </c>
-      <c r="L33" s="18">
+      <c r="L33" s="17">
         <v>30542.98</v>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="18">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="N33" s="20">
+      <c r="N33" s="19">
         <v>2.1320000000000002E-3</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="19">
         <v>0.05</v>
       </c>
-      <c r="P33" s="21">
+      <c r="P33" s="20">
         <v>1E-3</v>
       </c>
-      <c r="Q33" s="12"/>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
+      <c r="Q33" s="47">
+        <f t="shared" si="3"/>
+        <v>1511840.4945</v>
+      </c>
+      <c r="R33" s="48">
+        <f t="shared" si="1"/>
+        <v>1.2259428992208594</v>
+      </c>
+      <c r="S33" s="49">
+        <f t="shared" si="4"/>
+        <v>14.125308064097853</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="15">
         <v>15369836</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <v>16641580.289999999</v>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="16">
         <v>146123.65</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="16">
         <v>275905.56</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="16">
         <v>824999.73</v>
       </c>
-      <c r="L34" s="18">
+      <c r="L34" s="17">
         <v>23503.42</v>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="18">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="N34" s="20">
+      <c r="N34" s="19">
         <v>2.6650000000000003E-3</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="19">
         <v>0.05</v>
       </c>
-      <c r="P34" s="21">
+      <c r="P34" s="20">
         <v>2.8000000000000004E-3</v>
       </c>
-      <c r="Q34" s="12"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
+      <c r="Q34" s="47">
+        <f t="shared" si="3"/>
+        <v>832079.01450000005</v>
+      </c>
+      <c r="R34" s="48">
+        <f t="shared" si="1"/>
+        <v>1.0085809537174031</v>
+      </c>
+      <c r="S34" s="49">
+        <f t="shared" si="4"/>
+        <v>11.620864795492697</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="15">
         <v>1092201</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <v>1178225.1299999999</v>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="16">
         <v>14922.41</v>
       </c>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17">
+      <c r="J35" s="16"/>
+      <c r="K35" s="16">
         <v>64147.12</v>
       </c>
-      <c r="L35" s="18">
+      <c r="L35" s="17">
         <v>4881.04</v>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="18">
         <v>8.1000000000000013E-3</v>
       </c>
-      <c r="N35" s="20">
+      <c r="N35" s="19">
         <v>1.5990000000000002E-3</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="19">
         <v>0.05</v>
       </c>
-      <c r="P35" s="21">
+      <c r="P35" s="20">
         <v>1.55E-2</v>
       </c>
-      <c r="Q35" s="12"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="s">
+      <c r="Q35" s="47">
+        <f t="shared" si="3"/>
+        <v>58911.256499999996</v>
+      </c>
+      <c r="R35" s="48">
+        <f t="shared" si="1"/>
+        <v>0.91837726307899703</v>
+      </c>
+      <c r="S35" s="49">
+        <f t="shared" si="4"/>
+        <v>10.581538314956086</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="23" t="s">
+      <c r="C36" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="F36" s="23" t="s">
+      <c r="F36" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="24">
         <v>2861224</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="25">
         <v>3227731.96</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="25">
         <v>45634.55</v>
       </c>
-      <c r="J36" s="26">
+      <c r="J36" s="25">
         <v>68818.87</v>
       </c>
-      <c r="K36" s="26">
+      <c r="K36" s="25">
         <v>189660.15</v>
       </c>
-      <c r="L36" s="27">
+      <c r="L36" s="26">
         <v>5190.9679999999998</v>
       </c>
-      <c r="M36" s="28">
+      <c r="M36" s="27">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="N36" s="29">
+      <c r="N36" s="28">
         <v>3.1980000000000003E-3</v>
       </c>
-      <c r="O36" s="29">
+      <c r="O36" s="28">
         <v>0.05</v>
       </c>
-      <c r="P36" s="30">
+      <c r="P36" s="29">
         <v>1.2199999999999999E-2</v>
       </c>
-      <c r="Q36" s="12"/>
+      <c r="Q36" s="47">
+        <f t="shared" si="3"/>
+        <v>161386.598</v>
+      </c>
+      <c r="R36" s="48">
+        <f t="shared" si="1"/>
+        <v>0.85092518380903948</v>
+      </c>
+      <c r="S36" s="49">
+        <f t="shared" si="4"/>
+        <v>9.8043557888713622</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2924,4 +3352,2233 @@
     <customPr name="LastActive" r:id="rId2"/>
   </customProperties>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C87EBC-4A47-4FB5-B8C3-042AB9140873}">
+  <dimension ref="A1:T36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
+    <col min="9" max="12" width="15.6640625" style="1" customWidth="1"/>
+    <col min="13" max="15" width="13.33203125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.6640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.33203125" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="I1" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="40" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="43">
+        <v>100</v>
+      </c>
+      <c r="H2" s="43"/>
+      <c r="I2" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="45">
+        <v>20</v>
+      </c>
+      <c r="N2" s="45">
+        <v>100</v>
+      </c>
+      <c r="O2" s="45">
+        <v>15</v>
+      </c>
+      <c r="P2" s="46">
+        <v>10</v>
+      </c>
+      <c r="S2" s="48">
+        <f>MAX(R3:R19)</f>
+        <v>0</v>
+      </c>
+      <c r="T2" s="50">
+        <f>MAX(R20:R36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="32">
+        <v>19591959</v>
+      </c>
+      <c r="H3" s="33">
+        <v>23351606.629999999</v>
+      </c>
+      <c r="I3" s="33">
+        <v>340116.97</v>
+      </c>
+      <c r="J3" s="33">
+        <v>905066.28</v>
+      </c>
+      <c r="K3" s="33">
+        <v>1183687.8500000001</v>
+      </c>
+      <c r="L3" s="34">
+        <v>415908.174</v>
+      </c>
+      <c r="M3" s="18">
+        <v>0</v>
+      </c>
+      <c r="N3" s="19">
+        <v>0</v>
+      </c>
+      <c r="O3" s="19">
+        <v>0</v>
+      </c>
+      <c r="P3" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="47">
+        <f>H3*O3</f>
+        <v>0</v>
+      </c>
+      <c r="R3" s="48">
+        <f>IF(Q3/K3&gt;2,2,Q3/K3)</f>
+        <v>0</v>
+      </c>
+      <c r="S3" s="49" t="e">
+        <f>R3/$S$2*$O$2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="15">
+        <v>1938784</v>
+      </c>
+      <c r="H4" s="16">
+        <v>2507130.58</v>
+      </c>
+      <c r="I4" s="16">
+        <v>906.39</v>
+      </c>
+      <c r="J4" s="16">
+        <v>72053.38</v>
+      </c>
+      <c r="K4" s="16">
+        <v>134775</v>
+      </c>
+      <c r="L4" s="17">
+        <v>12052.344999999999</v>
+      </c>
+      <c r="M4" s="18">
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
+        <v>0</v>
+      </c>
+      <c r="O4" s="19">
+        <v>0</v>
+      </c>
+      <c r="P4" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="47">
+        <f t="shared" ref="Q4:Q36" si="0">H4*O4</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="48">
+        <f t="shared" ref="R4:R36" si="1">IF(Q4/K4&gt;2,2,Q4/K4)</f>
+        <v>0</v>
+      </c>
+      <c r="S4" s="49" t="e">
+        <f t="shared" ref="S4:S19" si="2">R4/$S$2*$O$2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="15">
+        <v>22755058</v>
+      </c>
+      <c r="H5" s="16">
+        <v>17154613.550000001</v>
+      </c>
+      <c r="I5" s="16">
+        <v>219251.72</v>
+      </c>
+      <c r="J5" s="16">
+        <v>26162.53</v>
+      </c>
+      <c r="K5" s="16">
+        <v>950479.86</v>
+      </c>
+      <c r="L5" s="17">
+        <v>355339.39600000001</v>
+      </c>
+      <c r="M5" s="18">
+        <v>0</v>
+      </c>
+      <c r="N5" s="19">
+        <v>0</v>
+      </c>
+      <c r="O5" s="19">
+        <v>0</v>
+      </c>
+      <c r="P5" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R5" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="15">
+        <v>2686986</v>
+      </c>
+      <c r="H6" s="16">
+        <v>3261158.66</v>
+      </c>
+      <c r="I6" s="16">
+        <v>11393.01</v>
+      </c>
+      <c r="J6" s="16">
+        <v>69063.679999999993</v>
+      </c>
+      <c r="K6" s="16">
+        <v>215080.68</v>
+      </c>
+      <c r="L6" s="17">
+        <v>10297.922</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
+        <v>0</v>
+      </c>
+      <c r="O6" s="19">
+        <v>0</v>
+      </c>
+      <c r="P6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="15">
+        <v>9091366</v>
+      </c>
+      <c r="H7" s="16">
+        <v>8996043.75</v>
+      </c>
+      <c r="I7" s="16">
+        <v>152767.69</v>
+      </c>
+      <c r="J7" s="16">
+        <v>7136.64</v>
+      </c>
+      <c r="K7" s="16">
+        <v>634099.98</v>
+      </c>
+      <c r="L7" s="17">
+        <v>280739.12400000001</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0</v>
+      </c>
+      <c r="N7" s="19">
+        <v>0</v>
+      </c>
+      <c r="O7" s="19">
+        <v>0</v>
+      </c>
+      <c r="P7" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="15">
+        <v>6743579</v>
+      </c>
+      <c r="H8" s="16">
+        <v>6642878.6900000004</v>
+      </c>
+      <c r="I8" s="16">
+        <v>3409.33</v>
+      </c>
+      <c r="J8" s="16">
+        <v>65470.52</v>
+      </c>
+      <c r="K8" s="16">
+        <v>407617.55</v>
+      </c>
+      <c r="L8" s="17">
+        <v>91207.59</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="19">
+        <v>0</v>
+      </c>
+      <c r="O8" s="19">
+        <v>0</v>
+      </c>
+      <c r="P8" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="15">
+        <v>15993683</v>
+      </c>
+      <c r="H9" s="16">
+        <v>16522919.58</v>
+      </c>
+      <c r="I9" s="16">
+        <v>146350.9</v>
+      </c>
+      <c r="J9" s="16">
+        <v>167073.5</v>
+      </c>
+      <c r="K9" s="16">
+        <v>4292</v>
+      </c>
+      <c r="L9" s="17">
+        <v>320983.74400000001</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="19">
+        <v>0</v>
+      </c>
+      <c r="O9" s="19">
+        <v>0</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="47">
+        <f>H9*O9</f>
+        <v>0</v>
+      </c>
+      <c r="R9" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="15">
+        <v>3868280</v>
+      </c>
+      <c r="H10" s="16">
+        <v>4053690.1</v>
+      </c>
+      <c r="I10" s="16">
+        <v>30464.93</v>
+      </c>
+      <c r="J10" s="16">
+        <v>67225.78</v>
+      </c>
+      <c r="K10" s="16">
+        <v>210065</v>
+      </c>
+      <c r="L10" s="17">
+        <v>37777.313999999998</v>
+      </c>
+      <c r="M10" s="18">
+        <v>0</v>
+      </c>
+      <c r="N10" s="19">
+        <v>0</v>
+      </c>
+      <c r="O10" s="19">
+        <v>0</v>
+      </c>
+      <c r="P10" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="15">
+        <v>19794522</v>
+      </c>
+      <c r="H11" s="16">
+        <v>20005520.420000002</v>
+      </c>
+      <c r="I11" s="16">
+        <v>188212.22</v>
+      </c>
+      <c r="J11" s="16">
+        <v>223063.28</v>
+      </c>
+      <c r="K11" s="16">
+        <v>6860</v>
+      </c>
+      <c r="L11" s="17">
+        <v>140024.65</v>
+      </c>
+      <c r="M11" s="18">
+        <v>0</v>
+      </c>
+      <c r="N11" s="19">
+        <v>0</v>
+      </c>
+      <c r="O11" s="19">
+        <v>0</v>
+      </c>
+      <c r="P11" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="15">
+        <v>21909086</v>
+      </c>
+      <c r="H12" s="16">
+        <v>22951289.809999999</v>
+      </c>
+      <c r="I12" s="16">
+        <v>208685.61</v>
+      </c>
+      <c r="J12" s="16">
+        <v>7435.1</v>
+      </c>
+      <c r="K12" s="16">
+        <v>16540</v>
+      </c>
+      <c r="L12" s="17">
+        <v>408158.78700000001</v>
+      </c>
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="19">
+        <v>0</v>
+      </c>
+      <c r="O12" s="19">
+        <v>0</v>
+      </c>
+      <c r="P12" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="15">
+        <v>17009357</v>
+      </c>
+      <c r="H13" s="16">
+        <v>17127476.359999999</v>
+      </c>
+      <c r="I13" s="16">
+        <v>124955.03</v>
+      </c>
+      <c r="J13" s="16">
+        <v>190824.85</v>
+      </c>
+      <c r="K13" s="16">
+        <v>13718</v>
+      </c>
+      <c r="L13" s="17">
+        <v>129564.88499999999</v>
+      </c>
+      <c r="M13" s="18">
+        <v>0</v>
+      </c>
+      <c r="N13" s="19">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19">
+        <v>0</v>
+      </c>
+      <c r="P13" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S13" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="15">
+        <v>24798734</v>
+      </c>
+      <c r="H14" s="16">
+        <v>26507855.93</v>
+      </c>
+      <c r="I14" s="16">
+        <v>93468.95</v>
+      </c>
+      <c r="J14" s="16">
+        <v>26600.69</v>
+      </c>
+      <c r="K14" s="16">
+        <v>475842</v>
+      </c>
+      <c r="L14" s="17">
+        <v>207175.95800000001</v>
+      </c>
+      <c r="M14" s="18">
+        <v>0</v>
+      </c>
+      <c r="N14" s="19">
+        <v>0</v>
+      </c>
+      <c r="O14" s="19">
+        <v>0</v>
+      </c>
+      <c r="P14" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R14" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="15">
+        <v>6856551</v>
+      </c>
+      <c r="H15" s="16">
+        <v>6716259.54</v>
+      </c>
+      <c r="I15" s="16">
+        <v>83542.95</v>
+      </c>
+      <c r="J15" s="16">
+        <v>134250.79999999999</v>
+      </c>
+      <c r="K15" s="16">
+        <v>226615</v>
+      </c>
+      <c r="L15" s="17">
+        <v>262618.62</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+      <c r="N15" s="19">
+        <v>0</v>
+      </c>
+      <c r="O15" s="19">
+        <v>0</v>
+      </c>
+      <c r="P15" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R15" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="15">
+        <v>30621195</v>
+      </c>
+      <c r="H16" s="16">
+        <v>32052691.809999999</v>
+      </c>
+      <c r="I16" s="16">
+        <v>186262.07</v>
+      </c>
+      <c r="J16" s="16">
+        <v>24274.43</v>
+      </c>
+      <c r="K16" s="16">
+        <v>1244568</v>
+      </c>
+      <c r="L16" s="17">
+        <v>332994.59499999997</v>
+      </c>
+      <c r="M16" s="18">
+        <v>0</v>
+      </c>
+      <c r="N16" s="19">
+        <v>0</v>
+      </c>
+      <c r="O16" s="19">
+        <v>0</v>
+      </c>
+      <c r="P16" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R16" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="15">
+        <v>17188836</v>
+      </c>
+      <c r="H17" s="16">
+        <v>17428018.870000001</v>
+      </c>
+      <c r="I17" s="16">
+        <v>116216.48</v>
+      </c>
+      <c r="J17" s="16">
+        <v>259230.85</v>
+      </c>
+      <c r="K17" s="16">
+        <v>431095</v>
+      </c>
+      <c r="L17" s="17">
+        <v>141745.95499999999</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0</v>
+      </c>
+      <c r="N17" s="19">
+        <v>0</v>
+      </c>
+      <c r="O17" s="19">
+        <v>0</v>
+      </c>
+      <c r="P17" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="15">
+        <v>1219932</v>
+      </c>
+      <c r="H18" s="16">
+        <v>1151560.95</v>
+      </c>
+      <c r="I18" s="16">
+        <v>31147.97</v>
+      </c>
+      <c r="J18" s="16">
+        <v>55662.48</v>
+      </c>
+      <c r="K18" s="16">
+        <v>8988</v>
+      </c>
+      <c r="L18" s="17">
+        <v>39011.692999999999</v>
+      </c>
+      <c r="M18" s="18">
+        <v>0</v>
+      </c>
+      <c r="N18" s="19">
+        <v>0</v>
+      </c>
+      <c r="O18" s="19">
+        <v>0</v>
+      </c>
+      <c r="P18" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="24">
+        <v>3312987</v>
+      </c>
+      <c r="H19" s="25">
+        <v>3213559.51</v>
+      </c>
+      <c r="I19" s="25">
+        <v>28816.78</v>
+      </c>
+      <c r="J19" s="25">
+        <v>3780.6</v>
+      </c>
+      <c r="K19" s="25">
+        <v>205547</v>
+      </c>
+      <c r="L19" s="26">
+        <v>68784.183000000005</v>
+      </c>
+      <c r="M19" s="27">
+        <v>0</v>
+      </c>
+      <c r="N19" s="28">
+        <v>0</v>
+      </c>
+      <c r="O19" s="28">
+        <v>0</v>
+      </c>
+      <c r="P19" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="49" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="6">
+        <v>21379072</v>
+      </c>
+      <c r="H20" s="7">
+        <v>22377804.719999999</v>
+      </c>
+      <c r="I20" s="7">
+        <v>278296.7</v>
+      </c>
+      <c r="J20" s="7">
+        <v>452006.75</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1129236.25</v>
+      </c>
+      <c r="L20" s="8">
+        <v>109023.978</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10">
+        <v>0</v>
+      </c>
+      <c r="P20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R20" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="49" t="e">
+        <f>R20/$T$2*$O$2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T20" s="48"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="15">
+        <v>2100233</v>
+      </c>
+      <c r="H21" s="16">
+        <v>2296569.0099999998</v>
+      </c>
+      <c r="I21" s="16">
+        <v>2450.86</v>
+      </c>
+      <c r="J21" s="16">
+        <v>22035.74</v>
+      </c>
+      <c r="K21" s="16">
+        <v>112435</v>
+      </c>
+      <c r="L21" s="17">
+        <v>16538.763999999999</v>
+      </c>
+      <c r="M21" s="18">
+        <v>0</v>
+      </c>
+      <c r="N21" s="19">
+        <v>0</v>
+      </c>
+      <c r="O21" s="19">
+        <v>0</v>
+      </c>
+      <c r="P21" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R21" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="49" t="e">
+        <f t="shared" ref="S21:S36" si="3">R21/$T$2*$O$2</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="15">
+        <v>6000000</v>
+      </c>
+      <c r="H22" s="16">
+        <v>8754757.2799999993</v>
+      </c>
+      <c r="I22" s="16">
+        <v>2613.98</v>
+      </c>
+      <c r="J22" s="16">
+        <v>11687.46</v>
+      </c>
+      <c r="K22" s="16">
+        <v>881288</v>
+      </c>
+      <c r="L22" s="17">
+        <v>4645.74</v>
+      </c>
+      <c r="M22" s="18">
+        <v>0</v>
+      </c>
+      <c r="N22" s="19">
+        <v>0</v>
+      </c>
+      <c r="O22" s="19">
+        <v>0</v>
+      </c>
+      <c r="P22" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="15">
+        <v>3232951</v>
+      </c>
+      <c r="H23" s="16">
+        <v>3156377.33</v>
+      </c>
+      <c r="I23" s="16">
+        <v>8713.2800000000007</v>
+      </c>
+      <c r="J23" s="16">
+        <v>96077.08</v>
+      </c>
+      <c r="K23" s="16">
+        <v>193900</v>
+      </c>
+      <c r="L23" s="17">
+        <v>22909.393</v>
+      </c>
+      <c r="M23" s="18">
+        <v>0</v>
+      </c>
+      <c r="N23" s="19">
+        <v>0</v>
+      </c>
+      <c r="O23" s="19">
+        <v>0</v>
+      </c>
+      <c r="P23" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="15">
+        <v>8508152</v>
+      </c>
+      <c r="H24" s="16">
+        <v>8782254.2200000007</v>
+      </c>
+      <c r="I24" s="16">
+        <v>114550.21</v>
+      </c>
+      <c r="J24" s="16">
+        <v>215004.99</v>
+      </c>
+      <c r="K24" s="16">
+        <v>560636.86</v>
+      </c>
+      <c r="L24" s="17">
+        <v>17399.486000000001</v>
+      </c>
+      <c r="M24" s="18">
+        <v>0</v>
+      </c>
+      <c r="N24" s="19">
+        <v>0</v>
+      </c>
+      <c r="O24" s="19">
+        <v>0</v>
+      </c>
+      <c r="P24" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="15">
+        <v>6150356</v>
+      </c>
+      <c r="H25" s="16">
+        <v>6331291.4800000004</v>
+      </c>
+      <c r="I25" s="16">
+        <v>848.46</v>
+      </c>
+      <c r="J25" s="16">
+        <v>55561.33</v>
+      </c>
+      <c r="K25" s="16">
+        <v>357491.39</v>
+      </c>
+      <c r="L25" s="17">
+        <v>7466.04</v>
+      </c>
+      <c r="M25" s="18">
+        <v>0</v>
+      </c>
+      <c r="N25" s="19">
+        <v>0</v>
+      </c>
+      <c r="O25" s="19">
+        <v>0</v>
+      </c>
+      <c r="P25" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="15">
+        <v>15306555</v>
+      </c>
+      <c r="H26" s="16">
+        <v>15570538.48</v>
+      </c>
+      <c r="I26" s="16">
+        <v>175447.9</v>
+      </c>
+      <c r="J26" s="16">
+        <v>272389.03000000003</v>
+      </c>
+      <c r="K26" s="16">
+        <v>787796.12</v>
+      </c>
+      <c r="L26" s="17">
+        <v>30519.866999999998</v>
+      </c>
+      <c r="M26" s="18">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="15">
+        <v>3762746</v>
+      </c>
+      <c r="H27" s="16">
+        <v>3787951.38</v>
+      </c>
+      <c r="I27" s="16">
+        <v>46493.04</v>
+      </c>
+      <c r="J27" s="16">
+        <v>76596.06</v>
+      </c>
+      <c r="K27" s="16">
+        <v>218845.31</v>
+      </c>
+      <c r="L27" s="17">
+        <v>7222.8</v>
+      </c>
+      <c r="M27" s="18">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="15">
+        <v>18026002</v>
+      </c>
+      <c r="H28" s="16">
+        <v>19295921.5</v>
+      </c>
+      <c r="I28" s="16">
+        <v>173219.16</v>
+      </c>
+      <c r="J28" s="16">
+        <v>10841.97</v>
+      </c>
+      <c r="K28" s="16">
+        <v>918662.31</v>
+      </c>
+      <c r="L28" s="17">
+        <v>19952.25</v>
+      </c>
+      <c r="M28" s="18">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G29" s="15">
+        <v>21282486</v>
+      </c>
+      <c r="H29" s="16">
+        <v>21928287.18</v>
+      </c>
+      <c r="I29" s="16">
+        <v>245143.75</v>
+      </c>
+      <c r="J29" s="16">
+        <v>258047.3</v>
+      </c>
+      <c r="K29" s="16">
+        <v>1075360.1000000001</v>
+      </c>
+      <c r="L29" s="17">
+        <v>30274.82</v>
+      </c>
+      <c r="M29" s="18">
+        <v>0</v>
+      </c>
+      <c r="N29" s="19">
+        <v>0</v>
+      </c>
+      <c r="O29" s="19">
+        <v>0</v>
+      </c>
+      <c r="P29" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="54">
+        <v>16421348</v>
+      </c>
+      <c r="H30" s="55">
+        <v>16592421.289999999</v>
+      </c>
+      <c r="I30" s="55">
+        <v>166414.34</v>
+      </c>
+      <c r="J30" s="55">
+        <v>21085.25</v>
+      </c>
+      <c r="K30" s="55">
+        <v>775214.89</v>
+      </c>
+      <c r="L30" s="56">
+        <v>24702.48</v>
+      </c>
+      <c r="M30" s="57">
+        <v>0</v>
+      </c>
+      <c r="N30" s="58">
+        <v>0</v>
+      </c>
+      <c r="O30" s="58">
+        <v>0</v>
+      </c>
+      <c r="P30" s="59">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="61">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="62" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="15">
+        <v>24394317</v>
+      </c>
+      <c r="H31" s="16">
+        <v>24732366.73</v>
+      </c>
+      <c r="I31" s="16">
+        <v>138177.79</v>
+      </c>
+      <c r="J31" s="16">
+        <v>19775.87</v>
+      </c>
+      <c r="K31" s="16">
+        <v>949887.36</v>
+      </c>
+      <c r="L31" s="17">
+        <v>20745.919999999998</v>
+      </c>
+      <c r="M31" s="18">
+        <v>0</v>
+      </c>
+      <c r="N31" s="19">
+        <v>0</v>
+      </c>
+      <c r="O31" s="19">
+        <v>0</v>
+      </c>
+      <c r="P31" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G32" s="15">
+        <v>7182566</v>
+      </c>
+      <c r="H32" s="16">
+        <v>6727481.3700000001</v>
+      </c>
+      <c r="I32" s="16">
+        <v>85377.279999999999</v>
+      </c>
+      <c r="J32" s="16">
+        <v>167922.88</v>
+      </c>
+      <c r="K32" s="16">
+        <v>464714.09</v>
+      </c>
+      <c r="L32" s="17">
+        <v>54583.16</v>
+      </c>
+      <c r="M32" s="18">
+        <v>0</v>
+      </c>
+      <c r="N32" s="19">
+        <v>0</v>
+      </c>
+      <c r="O32" s="19">
+        <v>0</v>
+      </c>
+      <c r="P32" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="15">
+        <v>28067946</v>
+      </c>
+      <c r="H33" s="16">
+        <v>30236809.890000001</v>
+      </c>
+      <c r="I33" s="16">
+        <v>235038.9</v>
+      </c>
+      <c r="J33" s="16">
+        <v>405668.69</v>
+      </c>
+      <c r="K33" s="16">
+        <v>1233206.29</v>
+      </c>
+      <c r="L33" s="17">
+        <v>30542.98</v>
+      </c>
+      <c r="M33" s="18">
+        <v>0</v>
+      </c>
+      <c r="N33" s="19">
+        <v>0</v>
+      </c>
+      <c r="O33" s="19">
+        <v>0</v>
+      </c>
+      <c r="P33" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="15">
+        <v>15369836</v>
+      </c>
+      <c r="H34" s="16">
+        <v>16641580.289999999</v>
+      </c>
+      <c r="I34" s="16">
+        <v>146123.65</v>
+      </c>
+      <c r="J34" s="16">
+        <v>275905.56</v>
+      </c>
+      <c r="K34" s="16">
+        <v>824999.73</v>
+      </c>
+      <c r="L34" s="17">
+        <v>23503.42</v>
+      </c>
+      <c r="M34" s="18">
+        <v>0</v>
+      </c>
+      <c r="N34" s="19">
+        <v>0</v>
+      </c>
+      <c r="O34" s="19">
+        <v>0</v>
+      </c>
+      <c r="P34" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="15">
+        <v>1092201</v>
+      </c>
+      <c r="H35" s="16">
+        <v>1178225.1299999999</v>
+      </c>
+      <c r="I35" s="16">
+        <v>14922.41</v>
+      </c>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16">
+        <v>64147.12</v>
+      </c>
+      <c r="L35" s="17">
+        <v>4881.04</v>
+      </c>
+      <c r="M35" s="18">
+        <v>0</v>
+      </c>
+      <c r="N35" s="19">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19">
+        <v>0</v>
+      </c>
+      <c r="P35" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" s="24">
+        <v>2861224</v>
+      </c>
+      <c r="H36" s="25">
+        <v>3227731.96</v>
+      </c>
+      <c r="I36" s="25">
+        <v>45634.55</v>
+      </c>
+      <c r="J36" s="25">
+        <v>68818.87</v>
+      </c>
+      <c r="K36" s="25">
+        <v>189660.15</v>
+      </c>
+      <c r="L36" s="26">
+        <v>5190.9679999999998</v>
+      </c>
+      <c r="M36" s="27">
+        <v>0</v>
+      </c>
+      <c r="N36" s="28">
+        <v>0</v>
+      </c>
+      <c r="O36" s="28">
+        <v>0</v>
+      </c>
+      <c r="P36" s="29">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="48">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="49" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <customProperties>
+    <customPr name="LastActive" r:id="rId2"/>
+  </customProperties>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\odoo\custom_addons\com\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\usr\odoo18\custom_addons\com\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1BB96D-9BE5-4B57-B5BE-ECC65690BD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD22BD56-5CBB-4C45-944D-2500ED839D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="7200" windowWidth="35148" windowHeight="17352" xr2:uid="{FC0CED0A-9FCE-40DD-BE2D-447C6CC3E712}"/>
+    <workbookView xWindow="10410" yWindow="3045" windowWidth="28800" windowHeight="15345" xr2:uid="{FC0CED0A-9FCE-40DD-BE2D-447C6CC3E712}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId2"/>
+    <sheet name="Лист1 (2)" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="85">
   <si>
     <t>Белая Церковь</t>
   </si>
@@ -220,6 +224,78 @@
   </si>
   <si>
     <t>negative</t>
+  </si>
+  <si>
+    <t>Регион</t>
+  </si>
+  <si>
+    <t>Выторг</t>
+  </si>
+  <si>
+    <t>Списания</t>
+  </si>
+  <si>
+    <t>Недостачи инвент</t>
+  </si>
+  <si>
+    <t>Зарплаты</t>
+  </si>
+  <si>
+    <t>Магазин</t>
+  </si>
+  <si>
+    <t>Выторг1недели</t>
+  </si>
+  <si>
+    <t>Выторг2недели</t>
+  </si>
+  <si>
+    <t>Списания1недели</t>
+  </si>
+  <si>
+    <t>Списания2недели</t>
+  </si>
+  <si>
+    <t>Недостачи инвент1неделя</t>
+  </si>
+  <si>
+    <t>Недостачи инвент2неделя</t>
+  </si>
+  <si>
+    <t>Проц недост инвент</t>
+  </si>
+  <si>
+    <t>Зарплаты прод1 неделя</t>
+  </si>
+  <si>
+    <t>Зарплаты прод2 неделя</t>
+  </si>
+  <si>
+    <t>Проц зарплат</t>
+  </si>
+  <si>
+    <t>113 БЦ (ДАН)</t>
+  </si>
+  <si>
+    <t>001 Днепр Транзитный</t>
+  </si>
+  <si>
+    <t>013 Борисполь</t>
+  </si>
+  <si>
+    <t>112 Борисполь</t>
+  </si>
+  <si>
+    <t>132 Борисполь</t>
+  </si>
+  <si>
+    <t>211 Богодухов</t>
+  </si>
+  <si>
+    <t>234 Богодухов Кондитерка</t>
+  </si>
+  <si>
+    <t>Разом</t>
   </si>
 </sst>
 </file>
@@ -232,7 +308,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₴_-;\-* #,##0.00\ _₴_-;_-* &quot;-&quot;??\ _₴_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,8 +346,20 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -314,8 +402,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="54"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -609,13 +727,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="31"/>
+      </left>
+      <right style="thin">
+        <color indexed="31"/>
+      </right>
+      <top style="thin">
+        <color indexed="31"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="31"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="54"/>
+      </left>
+      <right style="thin">
+        <color indexed="54"/>
+      </right>
+      <top style="thin">
+        <color indexed="54"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="54"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -790,9 +939,61 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="10" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="12" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="9" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный_Лист2" xfId="3" xr:uid="{A9E29F9F-DE18-4BEA-8688-145E7F08D944}"/>
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
@@ -1127,23 +1328,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDAC6E24-B730-4B07-BF1F-2046EA212C85}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
-    <col min="9" max="12" width="15.6640625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.33203125" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" customWidth="1"/>
+    <col min="9" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="15" width="13.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
@@ -1193,7 +1394,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -1230,16 +1431,16 @@
       </c>
       <c r="S2" s="48">
         <f>MAX(R3:R19)</f>
-        <v>2</v>
+        <v>1.855902181806578</v>
       </c>
       <c r="T2" s="50">
         <f>MAX(R20:R36)</f>
         <v>1.3018578713375026</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>59</v>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="64">
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>0</v>
@@ -1259,16 +1460,20 @@
       <c r="G3" s="32">
         <v>19591959</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="7">
+        <f>VLOOKUP(E3,Лист2!A:K,3,0)</f>
         <v>23351606.629999999</v>
       </c>
-      <c r="I3" s="33">
+      <c r="I3" s="7">
+        <f>VLOOKUP(E3,Лист2!A:K,5,0)</f>
         <v>340116.97</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="7">
+        <f>VLOOKUP(E3,Лист2!A:K,7,0)</f>
         <v>905066.28</v>
       </c>
-      <c r="K3" s="33">
+      <c r="K3" s="7">
+        <f>VLOOKUP(E3,Лист2!A:K,10,0)</f>
         <v>1183687.8500000001</v>
       </c>
       <c r="L3" s="34">
@@ -1296,12 +1501,12 @@
       </c>
       <c r="S3" s="49">
         <f>R3/$S$2*$O$2</f>
-        <v>7.3979406701268413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>59</v>
+        <v>7.9723389978727379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="65">
+        <v>1</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>0</v>
@@ -1322,15 +1527,19 @@
         <v>1938784</v>
       </c>
       <c r="H4" s="16">
+        <f>VLOOKUP(E4,Лист2!A:K,3,0)</f>
         <v>2507130.58</v>
       </c>
       <c r="I4" s="16">
+        <f>VLOOKUP(E4,Лист2!A:K,5,0)</f>
         <v>906.39</v>
       </c>
       <c r="J4" s="16">
+        <f>VLOOKUP(E4,Лист2!A:K,7,0)</f>
         <v>72053.38</v>
       </c>
       <c r="K4" s="16">
+        <f>VLOOKUP(E4,Лист2!A:K,10,0)</f>
         <v>134775</v>
       </c>
       <c r="L4" s="17">
@@ -1358,12 +1567,12 @@
       </c>
       <c r="S4" s="49">
         <f t="shared" ref="S4:S19" si="2">R4/$S$2*$O$2</f>
-        <v>6.9758780745687261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>59</v>
+        <v>7.517506195049835</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="65">
+        <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>0</v>
@@ -1384,15 +1593,19 @@
         <v>22755058</v>
       </c>
       <c r="H5" s="16">
+        <f>VLOOKUP(E5,Лист2!A:K,3,0)</f>
         <v>17154613.550000001</v>
       </c>
       <c r="I5" s="16">
+        <f>VLOOKUP(E5,Лист2!A:K,5,0)</f>
         <v>219251.72</v>
       </c>
       <c r="J5" s="16">
+        <f>VLOOKUP(E5,Лист2!A:K,7,0)</f>
         <v>26162.53</v>
       </c>
       <c r="K5" s="16">
+        <f>VLOOKUP(E5,Лист2!A:K,10,0)</f>
         <v>950479.86</v>
       </c>
       <c r="L5" s="17">
@@ -1420,12 +1633,12 @@
       </c>
       <c r="S5" s="49">
         <f t="shared" si="2"/>
-        <v>6.7681392862443195</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>59</v>
+        <v>7.2936379434136525</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="65">
+        <v>1</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>0</v>
@@ -1446,15 +1659,19 @@
         <v>2686986</v>
       </c>
       <c r="H6" s="16">
+        <f>VLOOKUP(E6,Лист2!A:K,3,0)</f>
         <v>3261158.66</v>
       </c>
       <c r="I6" s="16">
+        <f>VLOOKUP(E6,Лист2!A:K,5,0)</f>
         <v>11393.01</v>
       </c>
       <c r="J6" s="16">
+        <f>VLOOKUP(E6,Лист2!A:K,7,0)</f>
         <v>69063.679999999993</v>
       </c>
       <c r="K6" s="16">
+        <f>VLOOKUP(E6,Лист2!A:K,10,0)</f>
         <v>215080.68</v>
       </c>
       <c r="L6" s="17">
@@ -1482,12 +1699,12 @@
       </c>
       <c r="S6" s="49">
         <f t="shared" si="2"/>
-        <v>5.6859337505349163</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>59</v>
+        <v>6.1274067203262801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="65">
+        <v>1</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>5</v>
@@ -1508,15 +1725,19 @@
         <v>9091366</v>
       </c>
       <c r="H7" s="16">
+        <f>VLOOKUP(E7,Лист2!A:K,3,0)</f>
         <v>8996043.75</v>
       </c>
       <c r="I7" s="16">
+        <f>VLOOKUP(E7,Лист2!A:K,5,0)</f>
         <v>152767.69</v>
       </c>
       <c r="J7" s="16">
+        <f>VLOOKUP(E7,Лист2!A:K,7,0)</f>
         <v>7136.64</v>
       </c>
       <c r="K7" s="16">
+        <f>VLOOKUP(E7,Лист2!A:K,10,0)</f>
         <v>634099.98</v>
       </c>
       <c r="L7" s="17">
@@ -1544,12 +1765,12 @@
       </c>
       <c r="S7" s="49">
         <f t="shared" si="2"/>
-        <v>5.3201648204593859</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>59</v>
+        <v>5.7332383922094596</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="65">
+        <v>1</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>7</v>
@@ -1570,15 +1791,19 @@
         <v>6743579</v>
       </c>
       <c r="H8" s="16">
+        <f>VLOOKUP(E8,Лист2!A:K,3,0)</f>
         <v>6642878.6900000004</v>
       </c>
       <c r="I8" s="16">
+        <f>VLOOKUP(E8,Лист2!A:K,5,0)</f>
         <v>3409.33</v>
       </c>
       <c r="J8" s="16">
+        <f>VLOOKUP(E8,Лист2!A:K,7,0)</f>
         <v>65470.52</v>
       </c>
       <c r="K8" s="16">
+        <f>VLOOKUP(E8,Лист2!A:K,10,0)</f>
         <v>407617.55</v>
       </c>
       <c r="L8" s="17">
@@ -1606,12 +1831,12 @@
       </c>
       <c r="S8" s="49">
         <f t="shared" si="2"/>
-        <v>6.111315640727442</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>59</v>
+        <v>6.5858165377860027</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="65">
+        <v>1</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>9</v>
@@ -1632,16 +1857,20 @@
         <v>15993683</v>
       </c>
       <c r="H9" s="16">
+        <f>VLOOKUP(E9,Лист2!A:K,3,0)</f>
         <v>16522919.58</v>
       </c>
       <c r="I9" s="16">
-        <v>146350.9</v>
+        <f>VLOOKUP(E9,Лист2!A:K,5,0)</f>
+        <v>175749.88</v>
       </c>
       <c r="J9" s="16">
-        <v>167073.5</v>
+        <f>VLOOKUP(E9,Лист2!A:K,7,0)</f>
+        <v>167844</v>
       </c>
       <c r="K9" s="16">
-        <v>4292</v>
+        <f>VLOOKUP(E9,Лист2!A:K,10,0)</f>
+        <v>797764.07</v>
       </c>
       <c r="L9" s="17">
         <v>320983.74400000001</v>
@@ -1664,16 +1893,16 @@
       </c>
       <c r="R9" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.0355768203499063</v>
       </c>
       <c r="S9" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>59</v>
+        <v>8.3698658568997306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="65">
+        <v>1</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>9</v>
@@ -1694,16 +1923,20 @@
         <v>3868280</v>
       </c>
       <c r="H10" s="16">
+        <f>VLOOKUP(E10,Лист2!A:K,3,0)</f>
         <v>4053690.1</v>
       </c>
       <c r="I10" s="16">
-        <v>30464.93</v>
+        <f>VLOOKUP(E10,Лист2!A:K,5,0)</f>
+        <v>36903.589999999997</v>
       </c>
       <c r="J10" s="16">
+        <f>VLOOKUP(E10,Лист2!A:K,7,0)</f>
         <v>67225.78</v>
       </c>
       <c r="K10" s="16">
-        <v>210065</v>
+        <f>VLOOKUP(E10,Лист2!A:K,10,0)</f>
+        <v>210064.82</v>
       </c>
       <c r="L10" s="17">
         <v>37777.313999999998</v>
@@ -1726,16 +1959,16 @@
       </c>
       <c r="R10" s="48">
         <f t="shared" si="1"/>
-        <v>0.96486566062885304</v>
+        <v>0.96486648740136494</v>
       </c>
       <c r="S10" s="49">
         <f t="shared" si="2"/>
-        <v>7.236492454716398</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>59</v>
+        <v>7.7983621404723635</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="65">
+        <v>1</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>9</v>
@@ -1756,16 +1989,20 @@
         <v>19794522</v>
       </c>
       <c r="H11" s="16">
+        <f>VLOOKUP(E11,Лист2!A:K,3,0)</f>
         <v>20005520.420000002</v>
       </c>
       <c r="I11" s="16">
-        <v>188212.22</v>
+        <f>VLOOKUP(E11,Лист2!A:K,5,0)</f>
+        <v>214768.75</v>
       </c>
       <c r="J11" s="16">
+        <f>VLOOKUP(E11,Лист2!A:K,7,0)</f>
         <v>223063.28</v>
       </c>
       <c r="K11" s="16">
-        <v>6860</v>
+        <f>VLOOKUP(E11,Лист2!A:K,10,0)</f>
+        <v>977675.27</v>
       </c>
       <c r="L11" s="17">
         <v>140024.65</v>
@@ -1788,16 +2025,16 @@
       </c>
       <c r="R11" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.0231168279422678</v>
       </c>
       <c r="S11" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>59</v>
+        <v>8.2691601796572787</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="65">
+        <v>1</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>9</v>
@@ -1818,16 +2055,20 @@
         <v>21909086</v>
       </c>
       <c r="H12" s="16">
+        <f>VLOOKUP(E12,Лист2!A:K,3,0)</f>
         <v>22951289.809999999</v>
       </c>
       <c r="I12" s="16">
-        <v>208685.61</v>
+        <f>VLOOKUP(E12,Лист2!A:K,5,0)</f>
+        <v>240439.15</v>
       </c>
       <c r="J12" s="16">
-        <v>7435.1</v>
+        <f>VLOOKUP(E12,Лист2!A:K,7,0)</f>
+        <v>8926.9500000000007</v>
       </c>
       <c r="K12" s="16">
-        <v>16540</v>
+        <f>VLOOKUP(E12,Лист2!A:K,10,0)</f>
+        <v>1145454.28</v>
       </c>
       <c r="L12" s="17">
         <v>408158.78700000001</v>
@@ -1850,16 +2091,16 @@
       </c>
       <c r="R12" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.0018422476888384</v>
       </c>
       <c r="S12" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>59</v>
+        <v>8.0972121605592022</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="65">
+        <v>1</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>9</v>
@@ -1880,16 +2121,20 @@
         <v>17009357</v>
       </c>
       <c r="H13" s="16">
+        <f>VLOOKUP(E13,Лист2!A:K,3,0)</f>
         <v>17127476.359999999</v>
       </c>
       <c r="I13" s="16">
-        <v>124955.03</v>
+        <f>VLOOKUP(E13,Лист2!A:K,5,0)</f>
+        <v>161633.35999999999</v>
       </c>
       <c r="J13" s="16">
-        <v>190824.85</v>
+        <f>VLOOKUP(E13,Лист2!A:K,7,0)</f>
+        <v>191602.47</v>
       </c>
       <c r="K13" s="16">
-        <v>13718</v>
+        <f>VLOOKUP(E13,Лист2!A:K,10,0)</f>
+        <v>741443.19</v>
       </c>
       <c r="L13" s="17">
         <v>129564.88499999999</v>
@@ -1912,16 +2157,16 @@
       </c>
       <c r="R13" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.1550093514244835</v>
       </c>
       <c r="S13" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>59</v>
+        <v>9.3351580924930868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="65">
+        <v>1</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>9</v>
@@ -1942,16 +2187,20 @@
         <v>24798734</v>
       </c>
       <c r="H14" s="16">
+        <f>VLOOKUP(E14,Лист2!A:K,3,0)</f>
         <v>26507855.93</v>
       </c>
       <c r="I14" s="16">
-        <v>93468.95</v>
+        <f>VLOOKUP(E14,Лист2!A:K,5,0)</f>
+        <v>128859.79</v>
       </c>
       <c r="J14" s="16">
-        <v>26600.69</v>
+        <f>VLOOKUP(E14,Лист2!A:K,7,0)</f>
+        <v>37976.69</v>
       </c>
       <c r="K14" s="16">
-        <v>475842</v>
+        <f>VLOOKUP(E14,Лист2!A:K,10,0)</f>
+        <v>975832.29</v>
       </c>
       <c r="L14" s="17">
         <v>207175.95800000001</v>
@@ -1974,16 +2223,16 @@
       </c>
       <c r="R14" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.3582178106649865</v>
       </c>
       <c r="S14" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>59</v>
+        <v>10.977554398983997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="65">
+        <v>1</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
@@ -2004,16 +2253,20 @@
         <v>6856551</v>
       </c>
       <c r="H15" s="16">
+        <f>VLOOKUP(E15,Лист2!A:K,3,0)</f>
         <v>6716259.54</v>
       </c>
       <c r="I15" s="16">
-        <v>83542.95</v>
+        <f>VLOOKUP(E15,Лист2!A:K,5,0)</f>
+        <v>95607.75</v>
       </c>
       <c r="J15" s="16">
+        <f>VLOOKUP(E15,Лист2!A:K,7,0)</f>
         <v>134250.79999999999</v>
       </c>
       <c r="K15" s="16">
-        <v>226615</v>
+        <f>VLOOKUP(E15,Лист2!A:K,10,0)</f>
+        <v>525654.44999999995</v>
       </c>
       <c r="L15" s="17">
         <v>262618.62</v>
@@ -2036,16 +2289,16 @@
       </c>
       <c r="R15" s="48">
         <f t="shared" si="1"/>
-        <v>1.4818656178981975</v>
+        <v>0.63884739680221492</v>
       </c>
       <c r="S15" s="49">
         <f t="shared" si="2"/>
-        <v>11.113992134236481</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>59</v>
+        <v>5.1633707023853983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="65">
+        <v>1</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>9</v>
@@ -2066,16 +2319,20 @@
         <v>30621195</v>
       </c>
       <c r="H16" s="16">
+        <f>VLOOKUP(E16,Лист2!A:K,3,0)</f>
         <v>32052691.809999999</v>
       </c>
       <c r="I16" s="16">
-        <v>186262.07</v>
+        <f>VLOOKUP(E16,Лист2!A:K,5,0)</f>
+        <v>217352.95</v>
       </c>
       <c r="J16" s="16">
+        <f>VLOOKUP(E16,Лист2!A:K,7,0)</f>
         <v>24274.43</v>
       </c>
       <c r="K16" s="16">
-        <v>1244568</v>
+        <f>VLOOKUP(E16,Лист2!A:K,10,0)</f>
+        <v>1246929.07</v>
       </c>
       <c r="L16" s="17">
         <v>332994.59499999997</v>
@@ -2098,16 +2355,16 @@
       </c>
       <c r="R16" s="48">
         <f t="shared" si="1"/>
-        <v>1.2877035168026174</v>
+        <v>1.2852652400669429</v>
       </c>
       <c r="S16" s="49">
         <f t="shared" si="2"/>
-        <v>9.6577763760196298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>59</v>
+        <v>10.387928194705575</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="65">
+        <v>1</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>9</v>
@@ -2128,16 +2385,20 @@
         <v>17188836</v>
       </c>
       <c r="H17" s="16">
+        <f>VLOOKUP(E17,Лист2!A:K,3,0)</f>
         <v>17428018.870000001</v>
       </c>
       <c r="I17" s="16">
-        <v>116216.48</v>
+        <f>VLOOKUP(E17,Лист2!A:K,5,0)</f>
+        <v>144469.66</v>
       </c>
       <c r="J17" s="16">
-        <v>259230.85</v>
+        <f>VLOOKUP(E17,Лист2!A:K,7,0)</f>
+        <v>261264.45</v>
       </c>
       <c r="K17" s="16">
-        <v>431095</v>
+        <f>VLOOKUP(E17,Лист2!A:K,10,0)</f>
+        <v>893976.07</v>
       </c>
       <c r="L17" s="17">
         <v>141745.95499999999</v>
@@ -2160,16 +2421,16 @@
       </c>
       <c r="R17" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>0.97474750470669769</v>
       </c>
       <c r="S17" s="49">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>59</v>
+        <v>7.8782237091654475</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A18" s="65">
+        <v>1</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>9</v>
@@ -2190,16 +2451,20 @@
         <v>1219932</v>
       </c>
       <c r="H18" s="16">
+        <f>VLOOKUP(E18,Лист2!A:K,3,0)</f>
         <v>1151560.95</v>
       </c>
       <c r="I18" s="16">
-        <v>31147.97</v>
+        <f>VLOOKUP(E18,Лист2!A:K,5,0)</f>
+        <v>33622.300000000003</v>
       </c>
       <c r="J18" s="16">
+        <f>VLOOKUP(E18,Лист2!A:K,7,0)</f>
         <v>55662.48</v>
       </c>
       <c r="K18" s="16">
-        <v>8988</v>
+        <f>VLOOKUP(E18,Лист2!A:K,10,0)</f>
+        <v>31024.29</v>
       </c>
       <c r="L18" s="17">
         <v>39011.692999999999</v>
@@ -2222,16 +2487,16 @@
       </c>
       <c r="R18" s="48">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>1.855902181806578</v>
       </c>
       <c r="S18" s="49">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
-        <v>59</v>
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="66">
+        <v>1</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>9</v>
@@ -2252,16 +2517,20 @@
         <v>3312987</v>
       </c>
       <c r="H19" s="25">
+        <f>VLOOKUP(E19,Лист2!A:K,3,0)</f>
         <v>3213559.51</v>
       </c>
       <c r="I19" s="25">
-        <v>28816.78</v>
+        <f>VLOOKUP(E19,Лист2!A:K,5,0)</f>
+        <v>32154.19</v>
       </c>
       <c r="J19" s="25">
+        <f>VLOOKUP(E19,Лист2!A:K,7,0)</f>
         <v>3780.6</v>
       </c>
       <c r="K19" s="25">
-        <v>205547</v>
+        <f>VLOOKUP(E19,Лист2!A:K,10,0)</f>
+        <v>205546.67</v>
       </c>
       <c r="L19" s="26">
         <v>68784.183000000005</v>
@@ -2284,16 +2553,16 @@
       </c>
       <c r="R19" s="48">
         <f t="shared" si="1"/>
-        <v>0.78170917357100811</v>
+        <v>0.7817104285853913</v>
       </c>
       <c r="S19" s="49">
         <f t="shared" si="2"/>
-        <v>5.8628188017825611</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>58</v>
+        <v>6.3180358015242186</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="64">
+        <v>2</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>0</v>
@@ -2314,15 +2583,19 @@
         <v>21379072</v>
       </c>
       <c r="H20" s="7">
+        <f>VLOOKUP(E20,Лист2!A:K,2,0)</f>
         <v>22377804.719999999</v>
       </c>
       <c r="I20" s="7">
+        <f>VLOOKUP(E20,Лист2!A:K,4,0)</f>
         <v>278296.7</v>
       </c>
       <c r="J20" s="7">
+        <f>VLOOKUP(E20,Лист2!A:K,6,0)</f>
         <v>452006.75</v>
       </c>
       <c r="K20" s="7">
+        <f>VLOOKUP(E20,Лист2!A:K,9,0)</f>
         <v>1129236.25</v>
       </c>
       <c r="L20" s="8">
@@ -2354,9 +2627,9 @@
       </c>
       <c r="T20" s="48"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>58</v>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A21" s="65">
+        <v>2</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>0</v>
@@ -2377,15 +2650,19 @@
         <v>2100233</v>
       </c>
       <c r="H21" s="16">
+        <f>VLOOKUP(E21,Лист2!A:K,2,0)</f>
         <v>2296569.0099999998</v>
       </c>
       <c r="I21" s="16">
+        <f>VLOOKUP(E21,Лист2!A:K,4,0)</f>
         <v>2450.86</v>
       </c>
       <c r="J21" s="16">
+        <f>VLOOKUP(E21,Лист2!A:K,6,0)</f>
         <v>22035.74</v>
       </c>
       <c r="K21" s="16">
+        <f>VLOOKUP(E21,Лист2!A:K,9,0)</f>
         <v>112435</v>
       </c>
       <c r="L21" s="17">
@@ -2416,9 +2693,9 @@
         <v>11.767268579421925</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>58</v>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="65">
+        <v>2</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>0</v>
@@ -2439,15 +2716,19 @@
         <v>6000000</v>
       </c>
       <c r="H22" s="16">
+        <f>VLOOKUP(E22,Лист2!A:K,2,0)</f>
         <v>8754757.2799999993</v>
       </c>
       <c r="I22" s="16">
+        <f>VLOOKUP(E22,Лист2!A:K,4,0)</f>
         <v>2613.98</v>
       </c>
       <c r="J22" s="16">
+        <f>VLOOKUP(E22,Лист2!A:K,6,0)</f>
         <v>11687.46</v>
       </c>
       <c r="K22" s="16">
+        <f>VLOOKUP(E22,Лист2!A:K,9,0)</f>
         <v>881288</v>
       </c>
       <c r="L22" s="17">
@@ -2478,9 +2759,9 @@
         <v>5.7230026044093965</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>58</v>
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="65">
+        <v>2</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>0</v>
@@ -2501,15 +2782,19 @@
         <v>3232951</v>
       </c>
       <c r="H23" s="16">
+        <f>VLOOKUP(E23,Лист2!A:K,2,0)</f>
         <v>3156377.33</v>
       </c>
       <c r="I23" s="16">
+        <f>VLOOKUP(E23,Лист2!A:K,4,0)</f>
         <v>8713.2800000000007</v>
       </c>
       <c r="J23" s="16">
+        <f>VLOOKUP(E23,Лист2!A:K,6,0)</f>
         <v>96077.08</v>
       </c>
       <c r="K23" s="16">
+        <f>VLOOKUP(E23,Лист2!A:K,9,0)</f>
         <v>193900</v>
       </c>
       <c r="L23" s="17">
@@ -2540,9 +2825,9 @@
         <v>9.3779690807075173</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>58</v>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="65">
+        <v>2</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>5</v>
@@ -2563,15 +2848,19 @@
         <v>8508152</v>
       </c>
       <c r="H24" s="16">
+        <f>VLOOKUP(E24,Лист2!A:K,2,0)</f>
         <v>8782254.2200000007</v>
       </c>
       <c r="I24" s="16">
+        <f>VLOOKUP(E24,Лист2!A:K,4,0)</f>
         <v>114550.21</v>
       </c>
       <c r="J24" s="16">
+        <f>VLOOKUP(E24,Лист2!A:K,6,0)</f>
         <v>215004.99</v>
       </c>
       <c r="K24" s="16">
+        <f>VLOOKUP(E24,Лист2!A:K,9,0)</f>
         <v>560636.86</v>
       </c>
       <c r="L24" s="17">
@@ -2602,9 +2891,9 @@
         <v>9.0244770913149406</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>58</v>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A25" s="65">
+        <v>2</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>7</v>
@@ -2625,15 +2914,19 @@
         <v>6150356</v>
       </c>
       <c r="H25" s="16">
+        <f>VLOOKUP(E25,Лист2!A:K,2,0)</f>
         <v>6331291.4800000004</v>
       </c>
       <c r="I25" s="16">
+        <f>VLOOKUP(E25,Лист2!A:K,4,0)</f>
         <v>848.46</v>
       </c>
       <c r="J25" s="16">
+        <f>VLOOKUP(E25,Лист2!A:K,6,0)</f>
         <v>55561.33</v>
       </c>
       <c r="K25" s="16">
+        <f>VLOOKUP(E25,Лист2!A:K,9,0)</f>
         <v>357491.39</v>
       </c>
       <c r="L25" s="17">
@@ -2664,9 +2957,9 @@
         <v>10.20291836105079</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>58</v>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="65">
+        <v>2</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>9</v>
@@ -2687,15 +2980,19 @@
         <v>15306555</v>
       </c>
       <c r="H26" s="16">
+        <f>VLOOKUP(E26,Лист2!A:K,2,0)</f>
         <v>15570538.48</v>
       </c>
       <c r="I26" s="16">
+        <f>VLOOKUP(E26,Лист2!A:K,4,0)</f>
         <v>175447.9</v>
       </c>
       <c r="J26" s="16">
+        <f>VLOOKUP(E26,Лист2!A:K,6,0)</f>
         <v>272389.03000000003</v>
       </c>
       <c r="K26" s="16">
+        <f>VLOOKUP(E26,Лист2!A:K,9,0)</f>
         <v>787796.12</v>
       </c>
       <c r="L26" s="17">
@@ -2726,9 +3023,9 @@
         <v>11.386427486982939</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>58</v>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A27" s="65">
+        <v>2</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>9</v>
@@ -2749,15 +3046,19 @@
         <v>3762746</v>
       </c>
       <c r="H27" s="16">
+        <f>VLOOKUP(E27,Лист2!A:K,2,0)</f>
         <v>3787951.38</v>
       </c>
       <c r="I27" s="16">
+        <f>VLOOKUP(E27,Лист2!A:K,4,0)</f>
         <v>46493.04</v>
       </c>
       <c r="J27" s="16">
+        <f>VLOOKUP(E27,Лист2!A:K,6,0)</f>
         <v>76596.06</v>
       </c>
       <c r="K27" s="16">
+        <f>VLOOKUP(E27,Лист2!A:K,9,0)</f>
         <v>218845.31</v>
       </c>
       <c r="L27" s="17">
@@ -2788,9 +3089,9 @@
         <v>9.9715998477102694</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>58</v>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="65">
+        <v>2</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>9</v>
@@ -2811,15 +3112,19 @@
         <v>18026002</v>
       </c>
       <c r="H28" s="16">
+        <f>VLOOKUP(E28,Лист2!A:K,2,0)</f>
         <v>19295921.5</v>
       </c>
       <c r="I28" s="16">
+        <f>VLOOKUP(E28,Лист2!A:K,4,0)</f>
         <v>173219.16</v>
       </c>
       <c r="J28" s="16">
+        <f>VLOOKUP(E28,Лист2!A:K,6,0)</f>
         <v>10841.97</v>
       </c>
       <c r="K28" s="16">
+        <f>VLOOKUP(E28,Лист2!A:K,9,0)</f>
         <v>918662.31</v>
       </c>
       <c r="L28" s="17">
@@ -2850,9 +3155,9 @@
         <v>12.100611418294257</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>58</v>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="65">
+        <v>2</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>9</v>
@@ -2873,15 +3178,19 @@
         <v>21282486</v>
       </c>
       <c r="H29" s="16">
+        <f>VLOOKUP(E29,Лист2!A:K,2,0)</f>
         <v>21928287.18</v>
       </c>
       <c r="I29" s="16">
+        <f>VLOOKUP(E29,Лист2!A:K,4,0)</f>
         <v>245143.75</v>
       </c>
       <c r="J29" s="16">
+        <f>VLOOKUP(E29,Лист2!A:K,6,0)</f>
         <v>258047.3</v>
       </c>
       <c r="K29" s="16">
+        <f>VLOOKUP(E29,Лист2!A:K,9,0)</f>
         <v>1075360.1000000001</v>
       </c>
       <c r="L29" s="17">
@@ -2912,71 +3221,75 @@
         <v>11.747581912143081</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="52" t="s">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="65">
+        <v>2</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="52" t="s">
+      <c r="E30" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="G30" s="54">
+      <c r="G30" s="15">
         <v>16421348</v>
       </c>
-      <c r="H30" s="55">
+      <c r="H30" s="16">
+        <f>VLOOKUP(E30,Лист2!A:K,2,0)</f>
         <v>16592421.289999999</v>
       </c>
-      <c r="I30" s="55">
+      <c r="I30" s="16">
+        <f>VLOOKUP(E30,Лист2!A:K,4,0)</f>
         <v>166414.34</v>
       </c>
-      <c r="J30" s="55">
+      <c r="J30" s="16">
+        <f>VLOOKUP(E30,Лист2!A:K,6,0)</f>
         <v>21085.25</v>
       </c>
-      <c r="K30" s="55">
+      <c r="K30" s="16">
+        <f>VLOOKUP(E30,Лист2!A:K,9,0)</f>
         <v>775214.89</v>
       </c>
-      <c r="L30" s="56">
+      <c r="L30" s="17">
         <v>24702.48</v>
       </c>
-      <c r="M30" s="57">
+      <c r="M30" s="18">
         <v>6.8000000000000005E-3</v>
       </c>
-      <c r="N30" s="58">
+      <c r="N30" s="19">
         <v>1.0660000000000001E-3</v>
       </c>
-      <c r="O30" s="58">
+      <c r="O30" s="19">
         <v>0.05</v>
       </c>
-      <c r="P30" s="59">
+      <c r="P30" s="20">
         <v>3.9000000000000003E-3</v>
       </c>
-      <c r="Q30" s="60">
+      <c r="Q30" s="47">
         <f t="shared" si="3"/>
         <v>829621.06449999998</v>
       </c>
-      <c r="R30" s="61">
+      <c r="R30" s="48">
         <f t="shared" si="1"/>
         <v>1.0701820555846133</v>
       </c>
-      <c r="S30" s="62">
+      <c r="S30" s="49">
         <f t="shared" si="4"/>
         <v>12.330632388677689</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>58</v>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="65">
+        <v>2</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>9</v>
@@ -2997,15 +3310,19 @@
         <v>24394317</v>
       </c>
       <c r="H31" s="16">
+        <f>VLOOKUP(E31,Лист2!A:K,2,0)</f>
         <v>24732366.73</v>
       </c>
       <c r="I31" s="16">
+        <f>VLOOKUP(E31,Лист2!A:K,4,0)</f>
         <v>138177.79</v>
       </c>
       <c r="J31" s="16">
+        <f>VLOOKUP(E31,Лист2!A:K,6,0)</f>
         <v>19775.87</v>
       </c>
       <c r="K31" s="16">
+        <f>VLOOKUP(E31,Лист2!A:K,9,0)</f>
         <v>949887.36</v>
       </c>
       <c r="L31" s="17">
@@ -3036,9 +3353,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
-        <v>58</v>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="65">
+        <v>2</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>9</v>
@@ -3059,15 +3376,19 @@
         <v>7182566</v>
       </c>
       <c r="H32" s="16">
+        <f>VLOOKUP(E32,Лист2!A:K,2,0)</f>
         <v>6727481.3700000001</v>
       </c>
       <c r="I32" s="16">
+        <f>VLOOKUP(E32,Лист2!A:K,4,0)</f>
         <v>85377.279999999999</v>
       </c>
       <c r="J32" s="16">
+        <f>VLOOKUP(E32,Лист2!A:K,6,0)</f>
         <v>167922.88</v>
       </c>
       <c r="K32" s="16">
+        <f>VLOOKUP(E32,Лист2!A:K,9,0)</f>
         <v>464714.09</v>
       </c>
       <c r="L32" s="17">
@@ -3098,9 +3419,9 @@
         <v>8.3399674094048102</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
-        <v>58</v>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="65">
+        <v>2</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>9</v>
@@ -3121,15 +3442,19 @@
         <v>28067946</v>
       </c>
       <c r="H33" s="16">
+        <f>VLOOKUP(E33,Лист2!A:K,2,0)</f>
         <v>30236809.890000001</v>
       </c>
       <c r="I33" s="16">
+        <f>VLOOKUP(E33,Лист2!A:K,4,0)</f>
         <v>235038.9</v>
       </c>
       <c r="J33" s="16">
+        <f>VLOOKUP(E33,Лист2!A:K,6,0)</f>
         <v>405668.69</v>
       </c>
       <c r="K33" s="16">
+        <f>VLOOKUP(E33,Лист2!A:K,9,0)</f>
         <v>1233206.29</v>
       </c>
       <c r="L33" s="17">
@@ -3160,9 +3485,9 @@
         <v>14.125308064097853</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
-        <v>58</v>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="65">
+        <v>2</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>9</v>
@@ -3183,15 +3508,19 @@
         <v>15369836</v>
       </c>
       <c r="H34" s="16">
+        <f>VLOOKUP(E34,Лист2!A:K,2,0)</f>
         <v>16641580.289999999</v>
       </c>
       <c r="I34" s="16">
+        <f>VLOOKUP(E34,Лист2!A:K,4,0)</f>
         <v>146123.65</v>
       </c>
       <c r="J34" s="16">
+        <f>VLOOKUP(E34,Лист2!A:K,6,0)</f>
         <v>275905.56</v>
       </c>
       <c r="K34" s="16">
+        <f>VLOOKUP(E34,Лист2!A:K,9,0)</f>
         <v>824999.73</v>
       </c>
       <c r="L34" s="17">
@@ -3222,9 +3551,9 @@
         <v>11.620864795492697</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>58</v>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="65">
+        <v>2</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>9</v>
@@ -3245,13 +3574,19 @@
         <v>1092201</v>
       </c>
       <c r="H35" s="16">
+        <f>VLOOKUP(E35,Лист2!A:K,2,0)</f>
         <v>1178225.1299999999</v>
       </c>
       <c r="I35" s="16">
+        <f>VLOOKUP(E35,Лист2!A:K,4,0)</f>
         <v>14922.41</v>
       </c>
-      <c r="J35" s="16"/>
+      <c r="J35" s="16">
+        <f>VLOOKUP(E35,Лист2!A:K,6,0)</f>
+        <v>0</v>
+      </c>
       <c r="K35" s="16">
+        <f>VLOOKUP(E35,Лист2!A:K,9,0)</f>
         <v>64147.12</v>
       </c>
       <c r="L35" s="17">
@@ -3282,9 +3617,9 @@
         <v>10.581538314956086</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="21" t="s">
-        <v>58</v>
+    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="66">
+        <v>2</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>9</v>
@@ -3305,15 +3640,19 @@
         <v>2861224</v>
       </c>
       <c r="H36" s="25">
+        <f>VLOOKUP(E36,Лист2!A:K,2,0)</f>
         <v>3227731.96</v>
       </c>
       <c r="I36" s="25">
+        <f>VLOOKUP(E36,Лист2!A:K,4,0)</f>
         <v>45634.55</v>
       </c>
       <c r="J36" s="25">
+        <f>VLOOKUP(E36,Лист2!A:K,6,0)</f>
         <v>68818.87</v>
       </c>
       <c r="K36" s="25">
+        <f>VLOOKUP(E36,Лист2!A:K,9,0)</f>
         <v>189660.15</v>
       </c>
       <c r="L36" s="26">
@@ -3355,25 +3694,961 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC8091A-D3C7-4835-B8F0-F2DC9B1AE523}">
+  <dimension ref="A1:K27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+    </row>
+    <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.25">
+      <c r="A2" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="67" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="70">
+        <v>22377804.719999999</v>
+      </c>
+      <c r="C3" s="70">
+        <v>23351606.629999999</v>
+      </c>
+      <c r="D3" s="70">
+        <v>278296.7</v>
+      </c>
+      <c r="E3" s="70">
+        <v>340116.97</v>
+      </c>
+      <c r="F3" s="70">
+        <v>452006.75</v>
+      </c>
+      <c r="G3" s="70">
+        <v>905066.28</v>
+      </c>
+      <c r="H3" s="72">
+        <v>100.23</v>
+      </c>
+      <c r="I3" s="70">
+        <v>1129236.25</v>
+      </c>
+      <c r="J3" s="70">
+        <v>1183687.8500000001</v>
+      </c>
+      <c r="K3" s="71">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="70">
+        <v>2296569.0099999998</v>
+      </c>
+      <c r="C4" s="70">
+        <v>2507130.58</v>
+      </c>
+      <c r="D4" s="70">
+        <v>2450.86</v>
+      </c>
+      <c r="E4" s="73">
+        <v>906.39</v>
+      </c>
+      <c r="F4" s="70">
+        <v>22035.74</v>
+      </c>
+      <c r="G4" s="70">
+        <v>72053.38</v>
+      </c>
+      <c r="H4" s="72">
+        <v>226.98</v>
+      </c>
+      <c r="I4" s="70">
+        <v>112435</v>
+      </c>
+      <c r="J4" s="70">
+        <v>134775</v>
+      </c>
+      <c r="K4" s="71">
+        <v>19.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="70">
+        <v>8754757.2799999993</v>
+      </c>
+      <c r="C5" s="70">
+        <v>17154613.550000001</v>
+      </c>
+      <c r="D5" s="70">
+        <v>2613.98</v>
+      </c>
+      <c r="E5" s="70">
+        <v>219251.72</v>
+      </c>
+      <c r="F5" s="70">
+        <v>11687.46</v>
+      </c>
+      <c r="G5" s="70">
+        <v>26162.53</v>
+      </c>
+      <c r="H5" s="72">
+        <v>123.85</v>
+      </c>
+      <c r="I5" s="70">
+        <v>881288</v>
+      </c>
+      <c r="J5" s="70">
+        <v>950479.86</v>
+      </c>
+      <c r="K5" s="71">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="70">
+        <v>4542573.78</v>
+      </c>
+      <c r="C6" s="70">
+        <v>4838116.6100000003</v>
+      </c>
+      <c r="D6" s="70">
+        <v>11020.27</v>
+      </c>
+      <c r="E6" s="70">
+        <v>7451.91</v>
+      </c>
+      <c r="F6" s="70">
+        <v>92272.09</v>
+      </c>
+      <c r="G6" s="70">
+        <v>78740.600000000006</v>
+      </c>
+      <c r="H6" s="74">
+        <v>-14.66</v>
+      </c>
+      <c r="I6" s="70">
+        <v>482764.14</v>
+      </c>
+      <c r="J6" s="70">
+        <v>502046.11</v>
+      </c>
+      <c r="K6" s="71">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="70">
+        <v>3156377.33</v>
+      </c>
+      <c r="C7" s="70">
+        <v>3261158.66</v>
+      </c>
+      <c r="D7" s="70">
+        <v>8713.2800000000007</v>
+      </c>
+      <c r="E7" s="70">
+        <v>11393.01</v>
+      </c>
+      <c r="F7" s="70">
+        <v>96077.08</v>
+      </c>
+      <c r="G7" s="70">
+        <v>69063.679999999993</v>
+      </c>
+      <c r="H7" s="74">
+        <v>-28.12</v>
+      </c>
+      <c r="I7" s="70">
+        <v>193900</v>
+      </c>
+      <c r="J7" s="70">
+        <v>215080.68</v>
+      </c>
+      <c r="K7" s="71">
+        <v>10.92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="70">
+        <v>8782254.2200000007</v>
+      </c>
+      <c r="C8" s="70">
+        <v>8996043.75</v>
+      </c>
+      <c r="D8" s="70">
+        <v>114550.21</v>
+      </c>
+      <c r="E8" s="70">
+        <v>152767.69</v>
+      </c>
+      <c r="F8" s="70">
+        <v>215004.99</v>
+      </c>
+      <c r="G8" s="70">
+        <v>7136.64</v>
+      </c>
+      <c r="H8" s="74">
+        <v>-96.68</v>
+      </c>
+      <c r="I8" s="70">
+        <v>560636.86</v>
+      </c>
+      <c r="J8" s="70">
+        <v>634099.98</v>
+      </c>
+      <c r="K8" s="71">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="70">
+        <v>355110.48</v>
+      </c>
+      <c r="C9" s="70">
+        <v>588123</v>
+      </c>
+      <c r="D9" s="70">
+        <v>523268.55</v>
+      </c>
+      <c r="E9" s="70">
+        <v>777854.89</v>
+      </c>
+      <c r="F9" s="70">
+        <v>195120.68</v>
+      </c>
+      <c r="G9" s="70">
+        <v>212416.17</v>
+      </c>
+      <c r="H9" s="71">
+        <v>8.86</v>
+      </c>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+    </row>
+    <row r="10" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="70">
+        <v>7704969.7000000002</v>
+      </c>
+      <c r="C10" s="70">
+        <v>7938370.4100000001</v>
+      </c>
+      <c r="D10" s="70">
+        <v>2377.61</v>
+      </c>
+      <c r="E10" s="70">
+        <v>1774.77</v>
+      </c>
+      <c r="F10" s="70">
+        <v>129751.79</v>
+      </c>
+      <c r="G10" s="70">
+        <v>88712.51</v>
+      </c>
+      <c r="H10" s="74">
+        <v>-31.63</v>
+      </c>
+      <c r="I10" s="70">
+        <v>589193.38</v>
+      </c>
+      <c r="J10" s="70">
+        <v>631865.67000000004</v>
+      </c>
+      <c r="K10" s="71">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="70">
+        <v>6331291.4800000004</v>
+      </c>
+      <c r="C11" s="70">
+        <v>6642878.6900000004</v>
+      </c>
+      <c r="D11" s="73">
+        <v>848.46</v>
+      </c>
+      <c r="E11" s="70">
+        <v>3409.33</v>
+      </c>
+      <c r="F11" s="70">
+        <v>55561.33</v>
+      </c>
+      <c r="G11" s="70">
+        <v>65470.52</v>
+      </c>
+      <c r="H11" s="71">
+        <v>17.829999999999998</v>
+      </c>
+      <c r="I11" s="70">
+        <v>357491.39</v>
+      </c>
+      <c r="J11" s="70">
+        <v>407617.55</v>
+      </c>
+      <c r="K11" s="71">
+        <v>14.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="70">
+        <v>2678924.7999999998</v>
+      </c>
+      <c r="C12" s="70">
+        <v>2734748.75</v>
+      </c>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="70">
+        <v>70914.95</v>
+      </c>
+      <c r="G12" s="70">
+        <v>47903.25</v>
+      </c>
+      <c r="H12" s="74">
+        <v>-32.450000000000003</v>
+      </c>
+      <c r="I12" s="70">
+        <v>162365</v>
+      </c>
+      <c r="J12" s="70">
+        <v>163004</v>
+      </c>
+      <c r="K12" s="71">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="69" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="70">
+        <v>1946841.63</v>
+      </c>
+      <c r="C13" s="70">
+        <v>2039816.35</v>
+      </c>
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="70">
+        <v>86972.6</v>
+      </c>
+      <c r="G13" s="70">
+        <v>69615.789999999994</v>
+      </c>
+      <c r="H13" s="74">
+        <v>-19.96</v>
+      </c>
+      <c r="I13" s="70">
+        <v>113910</v>
+      </c>
+      <c r="J13" s="70">
+        <v>117730</v>
+      </c>
+      <c r="K13" s="71">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="67.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="70">
+        <v>15570538.48</v>
+      </c>
+      <c r="C14" s="70">
+        <v>16522919.58</v>
+      </c>
+      <c r="D14" s="70">
+        <v>175447.9</v>
+      </c>
+      <c r="E14" s="70">
+        <v>175749.88</v>
+      </c>
+      <c r="F14" s="70">
+        <v>272389.03000000003</v>
+      </c>
+      <c r="G14" s="70">
+        <v>167844</v>
+      </c>
+      <c r="H14" s="74">
+        <v>-38.380000000000003</v>
+      </c>
+      <c r="I14" s="70">
+        <v>787796.12</v>
+      </c>
+      <c r="J14" s="70">
+        <v>797764.07</v>
+      </c>
+      <c r="K14" s="71">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="70">
+        <v>3787951.38</v>
+      </c>
+      <c r="C15" s="70">
+        <v>4053690.1</v>
+      </c>
+      <c r="D15" s="70">
+        <v>46493.04</v>
+      </c>
+      <c r="E15" s="70">
+        <v>36903.589999999997</v>
+      </c>
+      <c r="F15" s="70">
+        <v>76596.06</v>
+      </c>
+      <c r="G15" s="70">
+        <v>67225.78</v>
+      </c>
+      <c r="H15" s="74">
+        <v>-12.23</v>
+      </c>
+      <c r="I15" s="70">
+        <v>218845.31</v>
+      </c>
+      <c r="J15" s="70">
+        <v>210064.82</v>
+      </c>
+      <c r="K15" s="74">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="70">
+        <v>1249323.73</v>
+      </c>
+      <c r="C16" s="70">
+        <v>1169466.93</v>
+      </c>
+      <c r="D16" s="76"/>
+      <c r="E16" s="76"/>
+      <c r="F16" s="70">
+        <v>45056</v>
+      </c>
+      <c r="G16" s="70">
+        <v>48539.49</v>
+      </c>
+      <c r="H16" s="71">
+        <v>7.73</v>
+      </c>
+      <c r="I16" s="70">
+        <v>78718</v>
+      </c>
+      <c r="J16" s="70">
+        <v>77745</v>
+      </c>
+      <c r="K16" s="74">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="70">
+        <v>19295921.5</v>
+      </c>
+      <c r="C17" s="70">
+        <v>20005520.420000002</v>
+      </c>
+      <c r="D17" s="70">
+        <v>173219.16</v>
+      </c>
+      <c r="E17" s="70">
+        <v>214768.75</v>
+      </c>
+      <c r="F17" s="70">
+        <v>10841.97</v>
+      </c>
+      <c r="G17" s="70">
+        <v>223063.28</v>
+      </c>
+      <c r="H17" s="75">
+        <v>1957.41</v>
+      </c>
+      <c r="I17" s="70">
+        <v>918662.31</v>
+      </c>
+      <c r="J17" s="70">
+        <v>977675.27</v>
+      </c>
+      <c r="K17" s="71">
+        <v>6.42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A18" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="70">
+        <v>21928287.18</v>
+      </c>
+      <c r="C18" s="70">
+        <v>22951289.809999999</v>
+      </c>
+      <c r="D18" s="70">
+        <v>245143.75</v>
+      </c>
+      <c r="E18" s="70">
+        <v>240439.15</v>
+      </c>
+      <c r="F18" s="70">
+        <v>258047.3</v>
+      </c>
+      <c r="G18" s="70">
+        <v>8926.9500000000007</v>
+      </c>
+      <c r="H18" s="74">
+        <v>-96.54</v>
+      </c>
+      <c r="I18" s="70">
+        <v>1075360.1000000001</v>
+      </c>
+      <c r="J18" s="70">
+        <v>1145454.28</v>
+      </c>
+      <c r="K18" s="71">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="70">
+        <v>16592421.289999999</v>
+      </c>
+      <c r="C19" s="70">
+        <v>17127476.359999999</v>
+      </c>
+      <c r="D19" s="70">
+        <v>166414.34</v>
+      </c>
+      <c r="E19" s="70">
+        <v>161633.35999999999</v>
+      </c>
+      <c r="F19" s="70">
+        <v>21085.25</v>
+      </c>
+      <c r="G19" s="70">
+        <v>191602.47</v>
+      </c>
+      <c r="H19" s="72">
+        <v>808.7</v>
+      </c>
+      <c r="I19" s="70">
+        <v>775214.89</v>
+      </c>
+      <c r="J19" s="70">
+        <v>741443.19</v>
+      </c>
+      <c r="K19" s="74">
+        <v>-4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="70">
+        <v>24732366.73</v>
+      </c>
+      <c r="C20" s="70">
+        <v>26507855.93</v>
+      </c>
+      <c r="D20" s="70">
+        <v>138177.79</v>
+      </c>
+      <c r="E20" s="70">
+        <v>128859.79</v>
+      </c>
+      <c r="F20" s="70">
+        <v>19775.87</v>
+      </c>
+      <c r="G20" s="70">
+        <v>37976.69</v>
+      </c>
+      <c r="H20" s="72">
+        <v>92.04</v>
+      </c>
+      <c r="I20" s="70">
+        <v>949887.36</v>
+      </c>
+      <c r="J20" s="70">
+        <v>975832.29</v>
+      </c>
+      <c r="K20" s="71">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="69" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="70">
+        <v>612280.73</v>
+      </c>
+      <c r="C21" s="70">
+        <v>624952.62</v>
+      </c>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="70">
+        <v>42742.55</v>
+      </c>
+      <c r="G21" s="70">
+        <v>25872.43</v>
+      </c>
+      <c r="H21" s="74">
+        <v>-39.47</v>
+      </c>
+      <c r="I21" s="70">
+        <v>35533</v>
+      </c>
+      <c r="J21" s="70">
+        <v>36768</v>
+      </c>
+      <c r="K21" s="71">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A22" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="70">
+        <v>6727481.3700000001</v>
+      </c>
+      <c r="C22" s="70">
+        <v>6716259.54</v>
+      </c>
+      <c r="D22" s="70">
+        <v>85377.279999999999</v>
+      </c>
+      <c r="E22" s="70">
+        <v>95607.75</v>
+      </c>
+      <c r="F22" s="70">
+        <v>167922.88</v>
+      </c>
+      <c r="G22" s="70">
+        <v>134250.79999999999</v>
+      </c>
+      <c r="H22" s="74">
+        <v>-20.05</v>
+      </c>
+      <c r="I22" s="70">
+        <v>464714.09</v>
+      </c>
+      <c r="J22" s="70">
+        <v>525654.44999999995</v>
+      </c>
+      <c r="K22" s="71">
+        <v>13.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="70">
+        <v>30236809.890000001</v>
+      </c>
+      <c r="C23" s="70">
+        <v>32052691.809999999</v>
+      </c>
+      <c r="D23" s="70">
+        <v>235038.9</v>
+      </c>
+      <c r="E23" s="70">
+        <v>217352.95</v>
+      </c>
+      <c r="F23" s="70">
+        <v>405668.69</v>
+      </c>
+      <c r="G23" s="70">
+        <v>24274.43</v>
+      </c>
+      <c r="H23" s="74">
+        <v>-94.02</v>
+      </c>
+      <c r="I23" s="70">
+        <v>1233206.29</v>
+      </c>
+      <c r="J23" s="70">
+        <v>1246929.07</v>
+      </c>
+      <c r="K23" s="71">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="70">
+        <v>16641580.289999999</v>
+      </c>
+      <c r="C24" s="70">
+        <v>17428018.870000001</v>
+      </c>
+      <c r="D24" s="70">
+        <v>146123.65</v>
+      </c>
+      <c r="E24" s="70">
+        <v>144469.66</v>
+      </c>
+      <c r="F24" s="70">
+        <v>275905.56</v>
+      </c>
+      <c r="G24" s="70">
+        <v>261264.45</v>
+      </c>
+      <c r="H24" s="74">
+        <v>-5.31</v>
+      </c>
+      <c r="I24" s="70">
+        <v>824999.73</v>
+      </c>
+      <c r="J24" s="70">
+        <v>893976.07</v>
+      </c>
+      <c r="K24" s="71">
+        <v>8.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="70">
+        <v>1178225.1299999999</v>
+      </c>
+      <c r="C25" s="70">
+        <v>1151560.95</v>
+      </c>
+      <c r="D25" s="70">
+        <v>14922.41</v>
+      </c>
+      <c r="E25" s="70">
+        <v>33622.300000000003</v>
+      </c>
+      <c r="F25" s="76"/>
+      <c r="G25" s="70">
+        <v>55662.48</v>
+      </c>
+      <c r="H25" s="72">
+        <v>100</v>
+      </c>
+      <c r="I25" s="70">
+        <v>64147.12</v>
+      </c>
+      <c r="J25" s="70">
+        <v>31024.29</v>
+      </c>
+      <c r="K25" s="74">
+        <v>-51.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A26" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="70">
+        <v>3227731.96</v>
+      </c>
+      <c r="C26" s="70">
+        <v>3213559.51</v>
+      </c>
+      <c r="D26" s="70">
+        <v>45634.55</v>
+      </c>
+      <c r="E26" s="70">
+        <v>32154.19</v>
+      </c>
+      <c r="F26" s="70">
+        <v>68818.87</v>
+      </c>
+      <c r="G26" s="70">
+        <v>3780.6</v>
+      </c>
+      <c r="H26" s="74">
+        <v>-94.51</v>
+      </c>
+      <c r="I26" s="70">
+        <v>189660.15</v>
+      </c>
+      <c r="J26" s="70">
+        <v>205546.67</v>
+      </c>
+      <c r="K26" s="71">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="78">
+        <v>230708394.09</v>
+      </c>
+      <c r="C27" s="78">
+        <v>249577869.41</v>
+      </c>
+      <c r="D27" s="78">
+        <v>2416132.69</v>
+      </c>
+      <c r="E27" s="78">
+        <v>2996488.05</v>
+      </c>
+      <c r="F27" s="78">
+        <v>3092255.49</v>
+      </c>
+      <c r="G27" s="78">
+        <v>2892625.2</v>
+      </c>
+      <c r="H27" s="80">
+        <v>117.49</v>
+      </c>
+      <c r="I27" s="78">
+        <v>12199964.49</v>
+      </c>
+      <c r="J27" s="78">
+        <v>12806264.17</v>
+      </c>
+      <c r="K27" s="79">
+        <v>3.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91C87EBC-4A47-4FB5-B8C3-042AB9140873}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="30.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="19.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
-    <col min="9" max="12" width="15.6640625" style="1" customWidth="1"/>
-    <col min="13" max="15" width="13.33203125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="16.6640625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.33203125" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" customWidth="1"/>
+    <col min="9" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="15" width="13.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>53</v>
       </c>
@@ -3423,7 +4698,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="41"/>
       <c r="B2" s="42"/>
       <c r="C2" s="42"/>
@@ -3467,7 +4742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>59</v>
       </c>
@@ -3529,7 +4804,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>59</v>
       </c>
@@ -3591,7 +4866,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>59</v>
       </c>
@@ -3653,7 +4928,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>59</v>
       </c>
@@ -3715,7 +4990,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>59</v>
       </c>
@@ -3777,7 +5052,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>59</v>
       </c>
@@ -3839,7 +5114,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>59</v>
       </c>
@@ -3901,7 +5176,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>59</v>
       </c>
@@ -3963,7 +5238,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>59</v>
       </c>
@@ -4025,7 +5300,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>59</v>
       </c>
@@ -4087,7 +5362,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>59</v>
       </c>
@@ -4149,7 +5424,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>59</v>
       </c>
@@ -4211,7 +5486,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>59</v>
       </c>
@@ -4273,7 +5548,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>59</v>
       </c>
@@ -4335,7 +5610,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>59</v>
       </c>
@@ -4397,7 +5672,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>59</v>
       </c>
@@ -4459,7 +5734,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
         <v>59</v>
       </c>
@@ -4521,7 +5796,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
@@ -4584,7 +5859,7 @@
       </c>
       <c r="T20" s="48"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>58</v>
       </c>
@@ -4646,7 +5921,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>58</v>
       </c>
@@ -4708,7 +5983,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>58</v>
       </c>
@@ -4770,7 +6045,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>58</v>
       </c>
@@ -4832,7 +6107,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>58</v>
       </c>
@@ -4894,7 +6169,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>58</v>
       </c>
@@ -4956,7 +6231,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>58</v>
       </c>
@@ -5018,7 +6293,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>58</v>
       </c>
@@ -5080,7 +6355,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>58</v>
       </c>
@@ -5142,7 +6417,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" s="63" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>58</v>
       </c>
@@ -5204,7 +6479,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>58</v>
       </c>
@@ -5266,7 +6541,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>58</v>
       </c>
@@ -5328,7 +6603,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>58</v>
       </c>
@@ -5390,7 +6665,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>58</v>
       </c>
@@ -5452,7 +6727,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>58</v>
       </c>
@@ -5512,7 +6787,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>58</v>
       </c>
